--- a/具身VC投资模拟器_题库v4.2.xlsx
+++ b/具身VC投资模拟器_题库v4.2.xlsx
@@ -2169,6 +2169,60 @@
     <t>主要不确定性</t>
   </si>
   <si>
+    <t>VC01</t>
+  </si>
+  <si>
+    <t>2016年天使轮（人工确认回报口径）</t>
+  </si>
+  <si>
+    <t>用户人工确认真实投资/最新估值倍率，保留并单独标识</t>
+  </si>
+  <si>
+    <t>亿元人民币</t>
+  </si>
+  <si>
+    <t>待补</t>
+  </si>
+  <si>
+    <t>沿用源表P列用户确认；用户未提供完整分子分母，不能反推凑数；用户确认依据最新轮估值；公开信息仅作旁证</t>
+  </si>
+  <si>
+    <t>人工确认值尚不能从公开数据独立复算；不冒充公开估值测算</t>
+  </si>
+  <si>
+    <t>VC41</t>
+  </si>
+  <si>
+    <t>2019年首轮</t>
+  </si>
+  <si>
+    <t>首轮投后估值 / 2026-10-15收盘总市值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>2019年首轮注资4,000万元对应投后估值3.75亿元，不将融资额作为估值。02513于2026-10-15收盘509.00港元，市值2,481.82亿港元，按0.8528折2,116.50亿元人民币。</t>
+  </si>
+  <si>
+    <t>汇率口径会影响倍率；未计后续稀释、优先权、税费与退出折价。来源：证券时报/新浪财经2026-01-08、Google Finance与Wise 2026-10-15。</t>
+  </si>
+  <si>
+    <t>VC37</t>
+  </si>
+  <si>
+    <t>2020-10天使轮</t>
+  </si>
+  <si>
+    <t>天使轮投后估值 / 2026-10-15收盘总市值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>2020-10天使轮投后估值4.80亿元；688802于2026-10-15收盘402.99元，Google Finance市值1,748.04亿元。两端同为人民币，1,748.04÷4.80。</t>
+  </si>
+  <si>
+    <t>早期投后估值引自审计资料转引；仅反映估值增长，未计持股稀释、优先权、税费与退出折价。来源：创业邦2025-12-17、Google Finance 2026-10-15。</t>
+  </si>
+  <si>
     <t>VC15</t>
   </si>
   <si>
@@ -2178,9 +2232,6 @@
     <t>早期公开估值与上市总市值之比（汇率折算；非投资者真实回报）</t>
   </si>
   <si>
-    <t>亿元人民币</t>
-  </si>
-  <si>
     <t>2026-10-15 15:11:07+08:00</t>
   </si>
   <si>
@@ -2190,6 +2241,189 @@
     <t>早期3600万元投前/投后未分；汇率目前为检索摘录；盘中估值随行情波动。±10%入口口径误差会使倍率约687—840倍。</t>
   </si>
   <si>
+    <t>VC12</t>
+  </si>
+  <si>
+    <t>天使轮</t>
+  </si>
+  <si>
+    <t>公开已完成估值已核实；早轮估值缺失，暂不计算</t>
+  </si>
+  <si>
+    <t>2025-03-25</t>
+  </si>
+  <si>
+    <t>首轮金额及持股比例均缺，不能从不明投资额假设10%—20%持股再套出一个倍数。；150亿元是最后可核到已完成融资且披露估值的节点；500亿元洽谈/收尾估值排除。</t>
+  </si>
+  <si>
+    <t>首轮估值待IT桔子历史融资参考估值或交易文件补查；后续已完成轮次是否另有估值也需核实。</t>
+  </si>
+  <si>
+    <t>VC40</t>
+  </si>
+  <si>
+    <t>2023-06天使轮</t>
+  </si>
+  <si>
+    <t>天使轮投后估值 / 最新已完成私募估值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>亿美元</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2023-06天使轮投后估值3亿美元；2026-10-06报道最后一轮私募已完成、公司估值约500亿美元。两端均为美元，500÷3。</t>
+  </si>
+  <si>
+    <t>终点报道未明确投前/投后，按“最新估值”参考；非现金退出，未计后续稀释、优先权、税费与退出折价。来源：澎湃新闻2026-06-08、彭博口径新浪财经2026-10-06。</t>
+  </si>
+  <si>
+    <t>VC46</t>
+  </si>
+  <si>
+    <t>2023年种子轮</t>
+  </si>
+  <si>
+    <t>已完成估值已核实；早轮估值不足，暂不计算</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>种子+天使+天使+累计数千万元，未得单轮金额和比例；不将三轮累计融资除以一个任意稀释率。；北京商报与甲子光年报道已完成本轮、估值超过20亿美元，取20亿美元下限。</t>
+  </si>
+  <si>
+    <t>首轮估值需补；以美元为共同币种，未来若入口人民币须注明统一汇率口径。</t>
+  </si>
+  <si>
+    <t>VC05</t>
+  </si>
+  <si>
+    <t>估值资料不足：不沿用v3教学倍数</t>
+  </si>
+  <si>
+    <t>首轮融资额190万/380万来源冲突，未披露投后估值或当轮持股；不能把任一融资金额直接当作进入估值。；2025-06最后一轮融资1.95亿元、投后52.95亿元；已上市主体2026-10-15约14:53市值129.9386亿港元，折111.35738亿元人民币。</t>
+  </si>
+  <si>
+    <t>待IT桔子首轮参考估值/招股书增资价及股本核对；若只有190万元融资额，缺新增持股比例，暂无有充分依据的估值中点。</t>
+  </si>
+  <si>
+    <t>VC49</t>
+  </si>
+  <si>
+    <t>首轮估值和终点估值均未披露，暂不计算</t>
+  </si>
+  <si>
+    <t>天使轮金额未披露；Pre-A的数千万融资额不能作为天使估值或替代估值。；9亿元为战略投资金额，75亿元为IPO拟募资额，均不能直接当作公司终点估值。</t>
+  </si>
+  <si>
+    <t>需补招股书、交易公告中的增资价格和投后股本后计算。</t>
+  </si>
+  <si>
+    <t>VC39</t>
+  </si>
+  <si>
+    <t>2020年天使轮（最早明确投后估值）</t>
+  </si>
+  <si>
+    <t>2020年天使轮投后估值16.46亿元；更早14亿元资料存在投前口径，未采用。688795于2026-10-15收盘321.27元，Google Finance市值1,668.60亿元。</t>
+  </si>
+  <si>
+    <t>采用最早明确投后口径；未计后续稀释、优先权、税费与退出折价。来源：36氪2025-12-05、Google Finance 2026-10-15。</t>
+  </si>
+  <si>
+    <t>VC27</t>
+  </si>
+  <si>
+    <t>最早可核实融资/交易时点</t>
+  </si>
+  <si>
+    <t>用户人工确认（非本轮独立核实）</t>
+  </si>
+  <si>
+    <t>用户确认2016年天使轮0.16亿元人民币；未取得该笔交易合同。；保留用户选定100亿元人民币终点，不改成其他估值。</t>
+  </si>
+  <si>
+    <t>用户确认的私人交易信息，未获取完整合同或估值日期，不伪装为公开证实。</t>
+  </si>
+  <si>
+    <t>VC33</t>
+  </si>
+  <si>
+    <t>天使轮，标准条款代理</t>
+  </si>
+  <si>
+    <t>奇绩公开标准条款代理早期估值/最新已披露估值下限（估算）</t>
+  </si>
+  <si>
+    <t>2026-03-06（最近有估值的公开轮次；后续有融资但估值未明）</t>
+  </si>
+  <si>
+    <t>奇绩官网公开30万美元换7%；0.003亿美元/7%=0.042857亿美元，按2021年美元兑人民币约6.45作跨币种折算=0.27643亿元。6.3–6.6汇率敏感区间对应约354–370倍。未宣称帕西尼实际合同必然适用标准条款。；创业邦原文2026-03-06明确投后估值超100亿元，取100亿元为已披露下限，算得约361.76倍；这只是该方法下的保守终点，不能称估值精确100亿。</t>
+  </si>
+  <si>
+    <t>较高：奇绩当前公开标准不等于2021帕西尼个别交易合同；汇率约值亦属估算；如IT桔子有早期参考估值应优先复核替换。</t>
+  </si>
+  <si>
+    <t>VC13</t>
+  </si>
+  <si>
+    <t>种子轮</t>
+  </si>
+  <si>
+    <t>最新可得已完成融资估值取披露下限；入口不足，暂不计算</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>只有数千万元融资范围，没有具体金额和出让比例；以任意融资中点÷任意持股比例会带来双重假设，暂不填倍率。；采用最近公开明确的超100亿元估值的100亿元下限，不冒充7月最新轮精确估值。</t>
+  </si>
+  <si>
+    <t>入口估值缺；终点为下限且日期滞后于最新融资。</t>
+  </si>
+  <si>
+    <t>VC16</t>
+  </si>
+  <si>
+    <t>天使轮（非更早种子轮）</t>
+  </si>
+  <si>
+    <t>最早可核实投资人披露估值与已完成融资估值下限之比</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>华民投创始合伙人崔斌在2026天使投资大会披露：估值1亿元时参与天使投资。；上证报确认B1完成且估值逾100亿；保守以100亿下限÷1亿=100倍。9月200亿Pre-IPO尚待交割，排除。</t>
+  </si>
+  <si>
+    <t>100倍是公开已完成轮次估值下限对应的保守数，不是最新Pre-IPO估值；投资人未明确1亿元为投前或投后。</t>
+  </si>
+  <si>
+    <t>VC08</t>
+  </si>
+  <si>
+    <t>A轮</t>
+  </si>
+  <si>
+    <t>公开A轮融资额 ÷ 明示持股假设所得的进入估值 / 2026-10-15公开市值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>以1亿美元按2017年平均约6.63元/美元折6.63亿元；假定该轮新增持股10%，则投后估值=6.63÷10%=66.3亿元。若新增持股为5%/15%，进入估值为132.6/44.2亿元，对应42.55/127.65倍。；腾讯证券15:24行情给出市值5,641.89亿元。</t>
+  </si>
+  <si>
+    <t>公开报道的A轮金额和具体交割币种、占股未在本次取得的原始交易文件中复核。</t>
+  </si>
+  <si>
+    <t>VC04</t>
+  </si>
+  <si>
+    <t>沿用用户按真实投资最新轮估值确认的80倍；原始起点金额未提供，不反推编造。；沿用用户最新轮估值口径，终点金额及日期未提供。</t>
+  </si>
+  <si>
     <t>VC43</t>
   </si>
   <si>
@@ -2199,27 +2433,345 @@
     <t>估值数据不足，暂不计算</t>
   </si>
   <si>
-    <t>待补</t>
-  </si>
-  <si>
     <t>没有早轮估值或出让比例，不能把融资额、注册资本或产品用户数当作估值。；没有同主体最新市值或可核投后估值。</t>
   </si>
   <si>
     <t>需以股权融资交易或上市文件补齐。</t>
   </si>
   <si>
+    <t>VC17</t>
+  </si>
+  <si>
+    <t>2024年种子轮（人工确认口径）</t>
+  </si>
+  <si>
+    <t>沿用源表P列用户确认；用户未提供完整分子分母，不能反推凑数；用户确认60倍按真实最新估值计算；公开20亿元是两轮融资金额而非估值，不据此凑分子。</t>
+  </si>
+  <si>
+    <t>VC50</t>
+  </si>
+  <si>
+    <t>天使阶段</t>
+  </si>
+  <si>
+    <t>首轮估值未核，暂不计算</t>
+  </si>
+  <si>
+    <t>2022（媒体估值线索）</t>
+  </si>
+  <si>
+    <t>首轮金额、估值和出让比例缺失，不能以任意天使融资额作为公司估值。；110亿元仅为历史媒体估值线索，缺交易文件与投前/投后定义；保留为待核参考，不能支撑倍数计算。</t>
+  </si>
+  <si>
+    <t>须通过IT桔子事件页、投资方公告或工商增资股本核对首轮和2022交易。</t>
+  </si>
+  <si>
+    <t>VC18</t>
+  </si>
+  <si>
+    <t>2023年天使轮首次交割</t>
+  </si>
+  <si>
+    <t>已完成投后估值下限已核实；首轮估值缺口暂不计算</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>千万美元融资为宽范围且含两次交割，未得出让比例；没有证据支持将融资额直接视为估值。；科创板日报明确本轮已完成、投后估值超200亿元，取200亿元下限。</t>
+  </si>
+  <si>
+    <t>入口估值待IT桔子或历史增资协议；200亿为终点下限。</t>
+  </si>
+  <si>
+    <t>VC42</t>
+  </si>
+  <si>
+    <t>早期</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2024-09 Pre-A仅披露“数亿元融资”，未披露估值，不能反推入口。2026-07 A3战略轮后有报道估值达到10亿美元，作为最新可信终点参考。</t>
+  </si>
+  <si>
+    <t>缺首轮投后估值，倍率保持待补。来源：亿欧2024-09-19、 新浪财经2026-08-04。</t>
+  </si>
+  <si>
+    <t>VC20</t>
+  </si>
+  <si>
+    <t>天使轮（最早已直接核实估值的轮次）</t>
+  </si>
+  <si>
+    <t>公开历史投后估值 / 2026-10-15市值：未稀释毛估值增长倍数</t>
+  </si>
+  <si>
+    <t>天使投资方同道齐创、道生资本、深创投、君溢创投等，投后1.5亿元；2022年末投后35.31亿元。；腾讯行情2026-10-15约14:54市值72.5046亿港元，按当日中间价0.8570折人民币</t>
+  </si>
+  <si>
+    <t>未核完整后续稀释；越疆种子轮1000万元估值尚未直接核招股书，故暂以天使1.5亿元作保守且已核的进入点。</t>
+  </si>
+  <si>
+    <t>VC48</t>
+  </si>
+  <si>
+    <t>设备业务早期阶段</t>
+  </si>
+  <si>
+    <t>没有可核的早轮估值或增资价格。；没有可核的末轮投后估值或市值。</t>
+  </si>
+  <si>
+    <t>需补IT桔子融资事件、投资方新闻稿或工商增资资料。</t>
+  </si>
+  <si>
+    <t>VC31</t>
+  </si>
+  <si>
+    <t>2017早期融资线索待核</t>
+  </si>
+  <si>
+    <t>缺起终点估值，暂不计算</t>
+  </si>
+  <si>
+    <t>缺真实融资定价与股比，不以数百万元/数千万元融资额冒充估值。；C1/C2数亿元合计融资是募集现金，不是企业估值；自媒体40亿尚未获得公司/机构背书。</t>
+  </si>
+  <si>
+    <t>早期和最新估值均需IT桔子/合同补证；原教学20倍删除，不能默认1倍或0倍。</t>
+  </si>
+  <si>
+    <t>VC02</t>
+  </si>
+  <si>
+    <t>用户明确确认首轮投后估值2亿元人民币。；用户明确确认最新估值80亿元人民币。</t>
+  </si>
+  <si>
+    <t>公开天使+轮2亿美元与用户首轮2亿元人民币不同，不可混同；用户数据沿用但日期、具体交易待合同佐证。</t>
+  </si>
+  <si>
+    <t>VC06</t>
+  </si>
+  <si>
+    <t>天使融资750万元是融资额，不是估值；未查获当轮新增持股比例或单位股权成本，故不硬设10%/20%稀释生成倍数。；2021-12 D轮融资5.8亿元、投后40.8亿元；2026-10-15约14:54港股02670市值46.8085亿港元，折40.114885亿元人民币。</t>
+  </si>
+  <si>
+    <t>待IT桔子首轮参考估值或招股书历史股本表；已知2021年C轮22.89亿、D轮40.8亿，可计算晚轮估值变化但不能替代早期回报。</t>
+  </si>
+  <si>
+    <t>VC10</t>
+  </si>
+  <si>
+    <t>天使轮（金额公开、估值以假设还原）</t>
+  </si>
+  <si>
+    <t>公开融资额 ÷ 明示持股假设所得的进入估值 / 公开报道的最新估值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>早期融资1,000万美元，假定本轮新增持股10%，投后估值=0.1亿美元÷10%=1亿美元；若占股5%/15%，进入估值为2/0.667亿美元，对应12.5/37.5倍。；采用2024年B轮后公开报道的约25亿美元估值；没有用B轮融资金额替代估值。</t>
+  </si>
+  <si>
+    <t>早期融资金额和25亿美元估值均需以IT桔子事件详情或公司交易文件进一步复核；截至截止日不声称为现金退出。</t>
+  </si>
+  <si>
+    <t>VC22</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>天使金额/比例未核实；2018年A轮5000万元融资额也不等于估值。若IT桔子有可见参考估值可另注明平台估算。；官网与新闻披露投后“突破100亿元”；以100亿元作为可见下界，不当成精确估值。</t>
+  </si>
+  <si>
+    <t>进入估值待核；终点100亿元是下界。无可辩护的首轮估值区间，倍数留空。</t>
+  </si>
+  <si>
+    <t>VC19</t>
+  </si>
+  <si>
+    <t>A1轮（最早可核实估值轮次）</t>
+  </si>
+  <si>
+    <t>据招股书，2016年A1轮融资4250万元、投后估值2.1亿元；2022-12 E1轮投后150亿元。；腾讯行情2026-10-15约14:54市值76.7254亿港元，按当日中间价0.8570折人民币</t>
+  </si>
+  <si>
+    <t>媒体直接引述招股书A1投后2.1亿元；2015创办期是否另有未公开轮次待核，因此称最早可核实估值轮次。未扣后续股本稀释。</t>
+  </si>
+  <si>
+    <t>VC30</t>
+  </si>
+  <si>
+    <t>定价增资（非首轮）</t>
+  </si>
+  <si>
+    <t>可核增资股份比例反推投后估值/收盘总市值</t>
+  </si>
+  <si>
+    <t>以2.5亿元认购531.25万股、投后9031.25万股：2.5/(531.25/9031.25)=42.5亿元。披露每股47.06元为四舍五入，优先用总对价和精确股数。；234元×183330125股÷1e8=428.99249亿元，约10.09倍。</t>
+  </si>
+  <si>
+    <t>2014谱润入股估值未取得；原表2016为游戏情景年，没有对应真实定价，因此改2018可核交易年。</t>
+  </si>
+  <si>
+    <t>VC45</t>
+  </si>
+  <si>
+    <t>2024-01天使轮</t>
+  </si>
+  <si>
+    <t>天使轮投后估值 / 最近公开投后估值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>2026-06（2026-09后续融资未披露新估值）</t>
+  </si>
+  <si>
+    <t>2024-01天使轮投后2.8亿元（另有投前2.3亿元口径，未混用）；2026-06 B+首轮后投后77.4亿元。2026-09后续融资未披露新估值，故不更新终点。</t>
+  </si>
+  <si>
+    <t>两端均为公开投后口径；未计后续稀释、优先权、税费与退出折价。来源：21财经、财新检索结果。</t>
+  </si>
+  <si>
+    <t>VC29</t>
+  </si>
+  <si>
+    <t>早期轮次估值待补</t>
+  </si>
+  <si>
+    <t>估值证据不足，暂不计算</t>
+  </si>
+  <si>
+    <t>2026-10-14美股收盘</t>
+  </si>
+  <si>
+    <t>已核2017 A轮1.1亿元人民币，但未见该轮出让股份或投后估值；不能将融资额当估值或任设20%稀释。；腾讯HSAI行情全股权市值21.90562亿美元；需与同币种入场估值比较，不能把人民币1.1亿融资直接作分母。</t>
+  </si>
+  <si>
+    <t>缺早期投后估值/持股比例，原表教学25倍作废而不默认1倍。</t>
+  </si>
+  <si>
+    <t>VC44</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2023-09天使轮与2024-09 A轮均未披露投后估值，不能反推入口。2026-10-05媒体报道称IPO前估值143亿元；与同期其他口径存在差异，作为待核参考终点。</t>
+  </si>
+  <si>
+    <t>缺首轮投后估值，倍率保持待补；143亿元为媒体报道、未得公司或交易文件交叉验证。</t>
+  </si>
+  <si>
+    <t>VC32</t>
+  </si>
+  <si>
+    <t>用户确认52亿元终点、20倍倍率，倒算起点52/20=2.6亿元；该2.6亿是代数反推值，不是公开首轮披露。；用户人工确认52亿元人民币；未提供估值日期，不编造日期。</t>
+  </si>
+  <si>
+    <t>VC14</t>
+  </si>
+  <si>
+    <t>2024年种子轮</t>
+  </si>
+  <si>
+    <t>公开已完成轮次估值；早轮估值缺失，暂不计算</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>近2亿元是种子+天使合计，既无法切分首轮金额，也没有首轮出让比例，不据此强估。；南都记者对已完成4月新一轮融资后估值的报道：200亿元。</t>
+  </si>
+  <si>
+    <t>首轮估值缺口；末轮估值是媒体采访口径。</t>
+  </si>
+  <si>
+    <t>VC07</t>
+  </si>
+  <si>
+    <t>战略投资（IT桔子可见最早轮次）</t>
+  </si>
+  <si>
+    <t>公开融资额 ÷ 明示持股假设所得的进入估值 / 2026-10-15公开市值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>以156.5亿元新增资金占投后10%作透明、可替换的基准，得到投后1,565亿元；10%不是已披露事实。若新增持股为5%/15%，进入估值为3,130/1,043.33亿元，对应9.45/28.36倍。；腾讯行情原始串的市值字段为29,590.68亿元；与当日“市值跌破3万亿”公开行情报道方向一致。</t>
+  </si>
+  <si>
+    <t>进入点不是公司成立时的首轮，只是IT桔子本次可复核的最早大额股权事件；取得该轮工商增资股数或交易文件后应替换10%假设。</t>
+  </si>
+  <si>
+    <t>VC21</t>
+  </si>
+  <si>
+    <t>2016年顺为资本早期定价轮（最早满足5000万元门槛）</t>
+  </si>
+  <si>
+    <t>公开历史投后估值 / 2026-10-15收盘总市值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>2015-03天津金米入股投后约4,380万元，低于5,000万元门槛，按规则排除。招股书口径的2016年顺为资本轮投后估值14.82亿元；2026-10-15收盘价103.10元×总股本259,567,776股=267.614377亿元。</t>
+  </si>
+  <si>
+    <t>入口采用首个满足门槛的公开定价轮，不等同于最早融资；未扣后续稀释、优先权、税费和流动性折价。来源：搜狐2023-01-16转引招股书、腾讯行情2026-10-15。</t>
+  </si>
+  <si>
+    <t>VC47</t>
+  </si>
+  <si>
+    <t>2019年A轮（最早公开可用估值）</t>
+  </si>
+  <si>
+    <t>A轮后估值 / 最新估值下限（跨币种折算）；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2019年A轮后报道称公司估值升至4亿美元；2026-03最新估值超120亿元人民币，按约7.2元/美元折超16.7亿美元，取16.7亿美元下限。</t>
+  </si>
+  <si>
+    <t>早期“升至4亿美元”未明确投前/投后，且跨币种折算仅作估算；终点为下限。未计后续稀释、优先权、税费与退出折价。来源：中国医药创新促进会、杭州政协及新浪财经检索结果。</t>
+  </si>
+  <si>
+    <t>VC35</t>
+  </si>
+  <si>
+    <t>2018年早期轮（最早公开可用估值下限）</t>
+  </si>
+  <si>
+    <t>早期估值下限 / 2026-10-15收盘总市值；按下限计算的最大倍率</t>
+  </si>
+  <si>
+    <t>2018年公开资料称公司估值超过10亿美元，取10亿美元下限；2026-10-15港股市值374.27亿港元，折约48.0亿美元。因入口为“超过10亿美元”，48÷10=4.80倍是上限。</t>
+  </si>
+  <si>
+    <t>入口投前/投后未明且为下限，真实倍数应低于4.80倍；未计后续稀释、优先权、税费与退出折价。来源：公开融资报道、2026-10-15港股行情。</t>
+  </si>
+  <si>
+    <t>VC38</t>
+  </si>
+  <si>
+    <t>2017-09 A1轮</t>
+  </si>
+  <si>
+    <t>A1轮投后估值折人民币 / 2026-10-15收盘总市值；未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>2017-09 A1轮投后5亿美元；按USD/HKD=7.80、HKD/CNY=0.8528折33.2592亿元人民币。09660于2026-10-15收盘3.84港元、市值607.99亿港元，折518.49亿元人民币。</t>
+  </si>
+  <si>
+    <t>汇率换算会影响倍率；未计后续稀释、优先权、税费与退出折价。来源：新浪财经2024-10-25、Google Finance与Wise 2026-10-15。</t>
+  </si>
+  <si>
     <t>VC23</t>
   </si>
   <si>
     <t>A轮/早期机构轮</t>
   </si>
   <si>
-    <t>估值资料不足：不沿用v3教学倍数</t>
-  </si>
-  <si>
-    <t>亿美元</t>
-  </si>
-  <si>
     <t>2018-05</t>
   </si>
   <si>
@@ -2229,70 +2781,25 @@
     <t>不能在2013年3亿美元尚未确认时写50倍；也不能把榜单估值或D类无息债权融资混同普通股定价。待IT桔子或权威历史交易补证。</t>
   </si>
   <si>
-    <t>VC06</t>
-  </si>
-  <si>
-    <t>天使轮</t>
-  </si>
-  <si>
-    <t>2026-10-15</t>
-  </si>
-  <si>
-    <t>天使融资750万元是融资额，不是估值；未查获当轮新增持股比例或单位股权成本，故不硬设10%/20%稀释生成倍数。；2021-12 D轮融资5.8亿元、投后40.8亿元；2026-10-15约14:54港股02670市值46.8085亿港元，折40.114885亿元人民币。</t>
-  </si>
-  <si>
-    <t>待IT桔子首轮参考估值或招股书历史股本表；已知2021年C轮22.89亿、D轮40.8亿，可计算晚轮估值变化但不能替代早期回报。</t>
-  </si>
-  <si>
-    <t>VC05</t>
-  </si>
-  <si>
-    <t>首轮融资额190万/380万来源冲突，未披露投后估值或当轮持股；不能把任一融资金额直接当作进入估值。；2025-06最后一轮融资1.95亿元、投后52.95亿元；已上市主体2026-10-15约14:53市值129.9386亿港元，折111.35738亿元人民币。</t>
-  </si>
-  <si>
-    <t>待IT桔子首轮参考估值/招股书增资价及股本核对；若只有190万元融资额，缺新增持股比例，暂无有充分依据的估值中点。</t>
-  </si>
-  <si>
-    <t>VC20</t>
-  </si>
-  <si>
-    <t>天使轮（最早已直接核实估值的轮次）</t>
-  </si>
-  <si>
-    <t>公开历史投后估值 / 2026-10-15市值：未稀释毛估值增长倍数</t>
-  </si>
-  <si>
-    <t>天使投资方同道齐创、道生资本、深创投、君溢创投等，投后1.5亿元；2022年末投后35.31亿元。；腾讯行情2026-10-15约14:54市值72.5046亿港元，按当日中间价0.8570折人民币</t>
-  </si>
-  <si>
-    <t>未核完整后续稀释；越疆种子轮1000万元估值尚未直接核招股书，故暂以天使1.5亿元作保守且已核的进入点。</t>
-  </si>
-  <si>
-    <t>VC48</t>
-  </si>
-  <si>
-    <t>设备业务早期阶段</t>
-  </si>
-  <si>
-    <t>没有可核的早轮估值或增资价格。；没有可核的末轮投后估值或市值。</t>
-  </si>
-  <si>
-    <t>需补IT桔子融资事件、投资方新闻稿或工商增资资料。</t>
-  </si>
-  <si>
-    <t>VC38</t>
-  </si>
-  <si>
-    <t>2017-09 A1轮</t>
-  </si>
-  <si>
-    <t>A1轮投后估值折人民币 / 2026-10-15收盘总市值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>2017-09 A1轮投后5亿美元；按USD/HKD=7.80、HKD/CNY=0.8528折33.2592亿元人民币。09660于2026-10-15收盘3.84港元、市值607.99亿港元，折518.49亿元人民币。</t>
-  </si>
-  <si>
-    <t>汇率换算会影响倍率；未计后续稀释、优先权、税费与退出折价。来源：新浪财经2024-10-25、Google Finance与Wise 2026-10-15。</t>
+    <t>VC03</t>
+  </si>
+  <si>
+    <t>2026年早期融资（用户真实投资口径）</t>
+  </si>
+  <si>
+    <t>VC11</t>
+  </si>
+  <si>
+    <t>科创板IPO（非首轮VC）</t>
+  </si>
+  <si>
+    <t>IPO发行价对应市值 / 2026-10-15公开市值；公开市场未稀释毛估值增长</t>
+  </si>
+  <si>
+    <t>发行价36.18元/股×发行前后总股本约8,037.437万股，得到约29.08亿元；这是可交易、可核的IPO进入点。；腾讯行情15:24显示股价284.60元、总股本80,374,370股，市值=284.60×80,374,370≈228.75亿元。</t>
+  </si>
+  <si>
+    <t>未把IPO倍率误称为早期VC回报；若需早期游戏进入点，须从招股书历史增资表补全真实单位股权成本。</t>
   </si>
   <si>
     <t>VC09</t>
@@ -2325,183 +2832,6 @@
     <t>需取得公开法院文书或管理人公告及历史增资交易价格后重算。</t>
   </si>
   <si>
-    <t>VC01</t>
-  </si>
-  <si>
-    <t>2016年天使轮（人工确认回报口径）</t>
-  </si>
-  <si>
-    <t>用户人工确认真实投资/最新估值倍率，保留并单独标识</t>
-  </si>
-  <si>
-    <t>沿用源表P列用户确认；用户未提供完整分子分母，不能反推凑数；用户确认依据最新轮估值；公开信息仅作旁证</t>
-  </si>
-  <si>
-    <t>人工确认值尚不能从公开数据独立复算；不冒充公开估值测算</t>
-  </si>
-  <si>
-    <t>VC49</t>
-  </si>
-  <si>
-    <t>首轮估值和终点估值均未披露，暂不计算</t>
-  </si>
-  <si>
-    <t>天使轮金额未披露；Pre-A的数千万融资额不能作为天使估值或替代估值。；9亿元为战略投资金额，75亿元为IPO拟募资额，均不能直接当作公司终点估值。</t>
-  </si>
-  <si>
-    <t>需补招股书、交易公告中的增资价格和投后股本后计算。</t>
-  </si>
-  <si>
-    <t>VC27</t>
-  </si>
-  <si>
-    <t>最早可核实融资/交易时点</t>
-  </si>
-  <si>
-    <t>用户人工确认（非本轮独立核实）</t>
-  </si>
-  <si>
-    <t>用户确认2016年天使轮0.16亿元人民币；未取得该笔交易合同。；保留用户选定100亿元人民币终点，不改成其他估值。</t>
-  </si>
-  <si>
-    <t>用户确认的私人交易信息，未获取完整合同或估值日期，不伪装为公开证实。</t>
-  </si>
-  <si>
-    <t>VC22</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>天使金额/比例未核实；2018年A轮5000万元融资额也不等于估值。若IT桔子有可见参考估值可另注明平台估算。；官网与新闻披露投后“突破100亿元”；以100亿元作为可见下界，不当成精确估值。</t>
-  </si>
-  <si>
-    <t>进入估值待核；终点100亿元是下界。无可辩护的首轮估值区间，倍数留空。</t>
-  </si>
-  <si>
-    <t>VC19</t>
-  </si>
-  <si>
-    <t>A1轮（最早可核实估值轮次）</t>
-  </si>
-  <si>
-    <t>据招股书，2016年A1轮融资4250万元、投后估值2.1亿元；2022-12 E1轮投后150亿元。；腾讯行情2026-10-15约14:54市值76.7254亿港元，按当日中间价0.8570折人民币</t>
-  </si>
-  <si>
-    <t>媒体直接引述招股书A1投后2.1亿元；2015创办期是否另有未公开轮次待核，因此称最早可核实估值轮次。未扣后续股本稀释。</t>
-  </si>
-  <si>
-    <t>VC30</t>
-  </si>
-  <si>
-    <t>定价增资（非首轮）</t>
-  </si>
-  <si>
-    <t>可核增资股份比例反推投后估值/收盘总市值</t>
-  </si>
-  <si>
-    <t>以2.5亿元认购531.25万股、投后9031.25万股：2.5/(531.25/9031.25)=42.5亿元。披露每股47.06元为四舍五入，优先用总对价和精确股数。；234元×183330125股÷1e8=428.99249亿元，约10.09倍。</t>
-  </si>
-  <si>
-    <t>2014谱润入股估值未取得；原表2016为游戏情景年，没有对应真实定价，因此改2018可核交易年。</t>
-  </si>
-  <si>
-    <t>VC29</t>
-  </si>
-  <si>
-    <t>早期轮次估值待补</t>
-  </si>
-  <si>
-    <t>估值证据不足，暂不计算</t>
-  </si>
-  <si>
-    <t>2026-10-14美股收盘</t>
-  </si>
-  <si>
-    <t>已核2017 A轮1.1亿元人民币，但未见该轮出让股份或投后估值；不能将融资额当估值或任设20%稀释。；腾讯HSAI行情全股权市值21.90562亿美元；需与同币种入场估值比较，不能把人民币1.1亿融资直接作分母。</t>
-  </si>
-  <si>
-    <t>缺早期投后估值/持股比例，原表教学25倍作废而不默认1倍。</t>
-  </si>
-  <si>
-    <t>VC21</t>
-  </si>
-  <si>
-    <t>2016年顺为资本早期定价轮（最早满足5000万元门槛）</t>
-  </si>
-  <si>
-    <t>公开历史投后估值 / 2026-10-15收盘总市值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>2015-03天津金米入股投后约4,380万元，低于5,000万元门槛，按规则排除。招股书口径的2016年顺为资本轮投后估值14.82亿元；2026-10-15收盘价103.10元×总股本259,567,776股=267.614377亿元。</t>
-  </si>
-  <si>
-    <t>入口采用首个满足门槛的公开定价轮，不等同于最早融资；未扣后续稀释、优先权、税费和流动性折价。来源：搜狐2023-01-16转引招股书、腾讯行情2026-10-15。</t>
-  </si>
-  <si>
-    <t>VC08</t>
-  </si>
-  <si>
-    <t>A轮</t>
-  </si>
-  <si>
-    <t>公开A轮融资额 ÷ 明示持股假设所得的进入估值 / 2026-10-15公开市值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>以1亿美元按2017年平均约6.63元/美元折6.63亿元；假定该轮新增持股10%，则投后估值=6.63÷10%=66.3亿元。若新增持股为5%/15%，进入估值为132.6/44.2亿元，对应42.55/127.65倍。；腾讯证券15:24行情给出市值5,641.89亿元。</t>
-  </si>
-  <si>
-    <t>公开报道的A轮金额和具体交割币种、占股未在本次取得的原始交易文件中复核。</t>
-  </si>
-  <si>
-    <t>VC31</t>
-  </si>
-  <si>
-    <t>2017早期融资线索待核</t>
-  </si>
-  <si>
-    <t>缺起终点估值，暂不计算</t>
-  </si>
-  <si>
-    <t>缺真实融资定价与股比，不以数百万元/数千万元融资额冒充估值。；C1/C2数亿元合计融资是募集现金，不是企业估值；自媒体40亿尚未获得公司/机构背书。</t>
-  </si>
-  <si>
-    <t>早期和最新估值均需IT桔子/合同补证；原教学20倍删除，不能默认1倍或0倍。</t>
-  </si>
-  <si>
-    <t>VC50</t>
-  </si>
-  <si>
-    <t>天使阶段</t>
-  </si>
-  <si>
-    <t>首轮估值未核，暂不计算</t>
-  </si>
-  <si>
-    <t>2022（媒体估值线索）</t>
-  </si>
-  <si>
-    <t>首轮金额、估值和出让比例缺失，不能以任意天使融资额作为公司估值。；110亿元仅为历史媒体估值线索，缺交易文件与投前/投后定义；保留为待核参考，不能支撑倍数计算。</t>
-  </si>
-  <si>
-    <t>须通过IT桔子事件页、投资方公告或工商增资股本核对首轮和2022交易。</t>
-  </si>
-  <si>
-    <t>VC35</t>
-  </si>
-  <si>
-    <t>2018年早期轮（最早公开可用估值下限）</t>
-  </si>
-  <si>
-    <t>早期估值下限 / 2026-10-15收盘总市值；按下限计算的最大倍率</t>
-  </si>
-  <si>
-    <t>2018年公开资料称公司估值超过10亿美元，取10亿美元下限；2026-10-15港股市值374.27亿港元，折约48.0亿美元。因入口为“超过10亿美元”，48÷10=4.80倍是上限。</t>
-  </si>
-  <si>
-    <t>入口投前/投后未明且为下限，真实倍数应低于4.80倍；未计后续稀释、优先权、税费与退出折价。来源：公开融资报道、2026-10-15港股行情。</t>
-  </si>
-  <si>
     <t>VC24</t>
   </si>
   <si>
@@ -2517,102 +2847,6 @@
     <t>不能因经营困难直接设0倍，不能用集团融资或估值搭配子公司结局；需独立交易资料及最终分配报告。</t>
   </si>
   <si>
-    <t>VC41</t>
-  </si>
-  <si>
-    <t>2019年首轮</t>
-  </si>
-  <si>
-    <t>首轮投后估值 / 2026-10-15收盘总市值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>2019年首轮注资4,000万元对应投后估值3.75亿元，不将融资额作为估值。02513于2026-10-15收盘509.00港元，市值2,481.82亿港元，按0.8528折2,116.50亿元人民币。</t>
-  </si>
-  <si>
-    <t>汇率口径会影响倍率；未计后续稀释、优先权、税费与退出折价。来源：证券时报/新浪财经2026-01-08、Google Finance与Wise 2026-10-15。</t>
-  </si>
-  <si>
-    <t>VC47</t>
-  </si>
-  <si>
-    <t>2019年A轮（最早公开可用估值）</t>
-  </si>
-  <si>
-    <t>A轮后估值 / 最新估值下限（跨币种折算）；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>2026-03</t>
-  </si>
-  <si>
-    <t>2019年A轮后报道称公司估值升至4亿美元；2026-03最新估值超120亿元人民币，按约7.2元/美元折超16.7亿美元，取16.7亿美元下限。</t>
-  </si>
-  <si>
-    <t>早期“升至4亿美元”未明确投前/投后，且跨币种折算仅作估算；终点为下限。未计后续稀释、优先权、税费与退出折价。来源：中国医药创新促进会、杭州政协及新浪财经检索结果。</t>
-  </si>
-  <si>
-    <t>VC37</t>
-  </si>
-  <si>
-    <t>2020-10天使轮</t>
-  </si>
-  <si>
-    <t>天使轮投后估值 / 2026-10-15收盘总市值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>2020-10天使轮投后估值4.80亿元；688802于2026-10-15收盘402.99元，Google Finance市值1,748.04亿元。两端同为人民币，1,748.04÷4.80。</t>
-  </si>
-  <si>
-    <t>早期投后估值引自审计资料转引；仅反映估值增长，未计持股稀释、优先权、税费与退出折价。来源：创业邦2025-12-17、Google Finance 2026-10-15。</t>
-  </si>
-  <si>
-    <t>VC39</t>
-  </si>
-  <si>
-    <t>2020年天使轮（最早明确投后估值）</t>
-  </si>
-  <si>
-    <t>2020年天使轮投后估值16.46亿元；更早14亿元资料存在投前口径，未采用。688795于2026-10-15收盘321.27元，Google Finance市值1,668.60亿元。</t>
-  </si>
-  <si>
-    <t>采用最早明确投后口径；未计后续稀释、优先权、税费与退出折价。来源：36氪2025-12-05、Google Finance 2026-10-15。</t>
-  </si>
-  <si>
-    <t>VC32</t>
-  </si>
-  <si>
-    <t>用户确认52亿元终点、20倍倍率，倒算起点52/20=2.6亿元；该2.6亿是代数反推值，不是公开首轮披露。；用户人工确认52亿元人民币；未提供估值日期，不编造日期。</t>
-  </si>
-  <si>
-    <t>VC07</t>
-  </si>
-  <si>
-    <t>战略投资（IT桔子可见最早轮次）</t>
-  </si>
-  <si>
-    <t>公开融资额 ÷ 明示持股假设所得的进入估值 / 2026-10-15公开市值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>以156.5亿元新增资金占投后10%作透明、可替换的基准，得到投后1,565亿元；10%不是已披露事实。若新增持股为5%/15%，进入估值为3,130/1,043.33亿元，对应9.45/28.36倍。；腾讯行情原始串的市值字段为29,590.68亿元；与当日“市值跌破3万亿”公开行情报道方向一致。</t>
-  </si>
-  <si>
-    <t>进入点不是公司成立时的首轮，只是IT桔子本次可复核的最早大额股权事件；取得该轮工商增资股数或交易文件后应替换10%假设。</t>
-  </si>
-  <si>
-    <t>VC11</t>
-  </si>
-  <si>
-    <t>科创板IPO（非首轮VC）</t>
-  </si>
-  <si>
-    <t>IPO发行价对应市值 / 2026-10-15公开市值；公开市场未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>发行价36.18元/股×发行前后总股本约8,037.437万股，得到约29.08亿元；这是可交易、可核的IPO进入点。；腾讯行情15:24显示股价284.60元、总股本80,374,370股，市值=284.60×80,374,370≈228.75亿元。</t>
-  </si>
-  <si>
-    <t>未把IPO倍率误称为早期VC回报；若需早期游戏进入点，须从招股书历史增资表补全真实单位股权成本。</t>
-  </si>
-  <si>
     <t>VC25</t>
   </si>
   <si>
@@ -2631,24 +2865,6 @@
     <t>缺首轮投后估值及最终清偿报告。即使存在资不抵债报道，也不能把真实回报擅定0倍。</t>
   </si>
   <si>
-    <t>VC33</t>
-  </si>
-  <si>
-    <t>天使轮，标准条款代理</t>
-  </si>
-  <si>
-    <t>奇绩公开标准条款代理早期估值/最新已披露估值下限（估算）</t>
-  </si>
-  <si>
-    <t>2026-03-06（最近有估值的公开轮次；后续有融资但估值未明）</t>
-  </si>
-  <si>
-    <t>奇绩官网公开30万美元换7%；0.003亿美元/7%=0.042857亿美元，按2021年美元兑人民币约6.45作跨币种折算=0.27643亿元。6.3–6.6汇率敏感区间对应约354–370倍。未宣称帕西尼实际合同必然适用标准条款。；创业邦原文2026-03-06明确投后估值超100亿元，取100亿元为已披露下限，算得约361.76倍；这只是该方法下的保守终点，不能称估值精确100亿。</t>
-  </si>
-  <si>
-    <t>较高：奇绩当前公开标准不等于2021帕西尼个别交易合同；汇率约值亦属估算；如IT桔子有早期参考估值应优先复核替换。</t>
-  </si>
-  <si>
     <t>VC34</t>
   </si>
   <si>
@@ -2662,222 +2878,6 @@
   </si>
   <si>
     <t>取得法院公开文书、工商注销/重整结果或投资人回收信息后，再按真实清偿率计算。</t>
-  </si>
-  <si>
-    <t>VC02</t>
-  </si>
-  <si>
-    <t>用户明确确认首轮投后估值2亿元人民币。；用户明确确认最新估值80亿元人民币。</t>
-  </si>
-  <si>
-    <t>公开天使+轮2亿美元与用户首轮2亿元人民币不同，不可混同；用户数据沿用但日期、具体交易待合同佐证。</t>
-  </si>
-  <si>
-    <t>VC10</t>
-  </si>
-  <si>
-    <t>天使轮（金额公开、估值以假设还原）</t>
-  </si>
-  <si>
-    <t>公开融资额 ÷ 明示持股假设所得的进入估值 / 公开报道的最新估值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>早期融资1,000万美元，假定本轮新增持股10%，投后估值=0.1亿美元÷10%=1亿美元；若占股5%/15%，进入估值为2/0.667亿美元，对应12.5/37.5倍。；采用2024年B轮后公开报道的约25亿美元估值；没有用B轮融资金额替代估值。</t>
-  </si>
-  <si>
-    <t>早期融资金额和25亿美元估值均需以IT桔子事件详情或公司交易文件进一步复核；截至截止日不声称为现金退出。</t>
-  </si>
-  <si>
-    <t>VC12</t>
-  </si>
-  <si>
-    <t>公开已完成估值已核实；早轮估值缺失，暂不计算</t>
-  </si>
-  <si>
-    <t>2025-03-25</t>
-  </si>
-  <si>
-    <t>首轮金额及持股比例均缺，不能从不明投资额假设10%—20%持股再套出一个倍数。；150亿元是最后可核到已完成融资且披露估值的节点；500亿元洽谈/收尾估值排除。</t>
-  </si>
-  <si>
-    <t>首轮估值待IT桔子历史融资参考估值或交易文件补查；后续已完成轮次是否另有估值也需核实。</t>
-  </si>
-  <si>
-    <t>VC40</t>
-  </si>
-  <si>
-    <t>2023-06天使轮</t>
-  </si>
-  <si>
-    <t>天使轮投后估值 / 最新已完成私募估值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>2026-10-06</t>
-  </si>
-  <si>
-    <t>2023-06天使轮投后估值3亿美元；2026-10-06报道最后一轮私募已完成、公司估值约500亿美元。两端均为美元，500÷3。</t>
-  </si>
-  <si>
-    <t>终点报道未明确投前/投后，按“最新估值”参考；非现金退出，未计后续稀释、优先权、税费与退出折价。来源：澎湃新闻2026-06-08、彭博口径新浪财经2026-10-06。</t>
-  </si>
-  <si>
-    <t>VC46</t>
-  </si>
-  <si>
-    <t>2023年种子轮</t>
-  </si>
-  <si>
-    <t>已完成估值已核实；早轮估值不足，暂不计算</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>种子+天使+天使+累计数千万元，未得单轮金额和比例；不将三轮累计融资除以一个任意稀释率。；北京商报与甲子光年报道已完成本轮、估值超过20亿美元，取20亿美元下限。</t>
-  </si>
-  <si>
-    <t>首轮估值需补；以美元为共同币种，未来若入口人民币须注明统一汇率口径。</t>
-  </si>
-  <si>
-    <t>VC13</t>
-  </si>
-  <si>
-    <t>种子轮</t>
-  </si>
-  <si>
-    <t>最新可得已完成融资估值取披露下限；入口不足，暂不计算</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>只有数千万元融资范围，没有具体金额和出让比例；以任意融资中点÷任意持股比例会带来双重假设，暂不填倍率。；采用最近公开明确的超100亿元估值的100亿元下限，不冒充7月最新轮精确估值。</t>
-  </si>
-  <si>
-    <t>入口估值缺；终点为下限且日期滞后于最新融资。</t>
-  </si>
-  <si>
-    <t>VC18</t>
-  </si>
-  <si>
-    <t>2023年天使轮首次交割</t>
-  </si>
-  <si>
-    <t>已完成投后估值下限已核实；首轮估值缺口暂不计算</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>千万美元融资为宽范围且含两次交割，未得出让比例；没有证据支持将融资额直接视为估值。；科创板日报明确本轮已完成、投后估值超200亿元，取200亿元下限。</t>
-  </si>
-  <si>
-    <t>入口估值待IT桔子或历史增资协议；200亿为终点下限。</t>
-  </si>
-  <si>
-    <t>VC44</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>2023-09天使轮与2024-09 A轮均未披露投后估值，不能反推入口。2026-10-05媒体报道称IPO前估值143亿元；与同期其他口径存在差异，作为待核参考终点。</t>
-  </si>
-  <si>
-    <t>缺首轮投后估值，倍率保持待补；143亿元为媒体报道、未得公司或交易文件交叉验证。</t>
-  </si>
-  <si>
-    <t>VC16</t>
-  </si>
-  <si>
-    <t>天使轮（非更早种子轮）</t>
-  </si>
-  <si>
-    <t>最早可核实投资人披露估值与已完成融资估值下限之比</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>华民投创始合伙人崔斌在2026天使投资大会披露：估值1亿元时参与天使投资。；上证报确认B1完成且估值逾100亿；保守以100亿下限÷1亿=100倍。9月200亿Pre-IPO尚待交割，排除。</t>
-  </si>
-  <si>
-    <t>100倍是公开已完成轮次估值下限对应的保守数，不是最新Pre-IPO估值；投资人未明确1亿元为投前或投后。</t>
-  </si>
-  <si>
-    <t>VC04</t>
-  </si>
-  <si>
-    <t>沿用用户按真实投资最新轮估值确认的80倍；原始起点金额未提供，不反推编造。；沿用用户最新轮估值口径，终点金额及日期未提供。</t>
-  </si>
-  <si>
-    <t>VC17</t>
-  </si>
-  <si>
-    <t>2024年种子轮（人工确认口径）</t>
-  </si>
-  <si>
-    <t>沿用源表P列用户确认；用户未提供完整分子分母，不能反推凑数；用户确认60倍按真实最新估值计算；公开20亿元是两轮融资金额而非估值，不据此凑分子。</t>
-  </si>
-  <si>
-    <t>VC42</t>
-  </si>
-  <si>
-    <t>早期</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>2024-09 Pre-A仅披露“数亿元融资”，未披露估值，不能反推入口。2026-07 A3战略轮后有报道估值达到10亿美元，作为最新可信终点参考。</t>
-  </si>
-  <si>
-    <t>缺首轮投后估值，倍率保持待补。来源：亿欧2024-09-19、 新浪财经2026-08-04。</t>
-  </si>
-  <si>
-    <t>VC45</t>
-  </si>
-  <si>
-    <t>2024-01天使轮</t>
-  </si>
-  <si>
-    <t>天使轮投后估值 / 最近公开投后估值；未稀释毛估值增长</t>
-  </si>
-  <si>
-    <t>2026-06（2026-09后续融资未披露新估值）</t>
-  </si>
-  <si>
-    <t>2024-01天使轮投后2.8亿元（另有投前2.3亿元口径，未混用）；2026-06 B+首轮后投后77.4亿元。2026-09后续融资未披露新估值，故不更新终点。</t>
-  </si>
-  <si>
-    <t>两端均为公开投后口径；未计后续稀释、优先权、税费与退出折价。来源：21财经、财新检索结果。</t>
-  </si>
-  <si>
-    <t>VC14</t>
-  </si>
-  <si>
-    <t>2024年种子轮</t>
-  </si>
-  <si>
-    <t>公开已完成轮次估值；早轮估值缺失，暂不计算</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>近2亿元是种子+天使合计，既无法切分首轮金额，也没有首轮出让比例，不据此强估。；南都记者对已完成4月新一轮融资后估值的报道：200亿元。</t>
-  </si>
-  <si>
-    <t>首轮估值缺口；末轮估值是媒体采访口径。</t>
-  </si>
-  <si>
-    <t>VC03</t>
-  </si>
-  <si>
-    <t>2026年早期融资（用户真实投资口径）</t>
   </si>
   <si>
     <t>VC28</t>
@@ -4422,9 +4422,6 @@
     <xf numFmtId="177" fontId="3" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="5" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4432,6 +4429,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4983,7 +4983,7 @@
       <c r="D2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="3">
@@ -4992,7 +4992,7 @@
       <c r="G2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="12" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -5010,13 +5010,13 @@
       <c r="M2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="12" t="s">
         <v>28</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="12" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="12" t="s">
         <v>34</v>
       </c>
       <c r="F3" s="3">
@@ -5060,10 +5060,10 @@
       <c r="M3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="12" t="s">
         <v>43</v>
       </c>
       <c r="P3" s="3">
@@ -5072,7 +5072,7 @@
       </c>
     </row>
     <row r="4" ht="128" customHeight="1" spans="1:16">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="12" t="s">
         <v>44</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -5111,10 +5111,10 @@
       <c r="M4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="12" t="s">
         <v>55</v>
       </c>
       <c r="P4" s="3">
@@ -7614,10 +7614,10 @@
         <v>677</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="C7" s="3">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>678</v>
@@ -7628,23 +7628,21 @@
       <c r="F7" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4">
-        <v>272.00714278</v>
-      </c>
-      <c r="I7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4">
+        <v>1035</v>
+      </c>
       <c r="J7" s="8">
         <v>1</v>
       </c>
       <c r="K7" s="4">
         <f>IF(ISNUMBER(I7),I7,IF(AND(ISNUMBER(G7),ISNUMBER(H7)),H7/G7,NA()))*J7</f>
-        <v>272.00714278</v>
+        <v>1035</v>
       </c>
       <c r="L7" s="8">
         <f>K7-1</f>
-        <v>271.00714278</v>
+        <v>1034</v>
       </c>
       <c r="M7" s="4">
         <f>$B$2</f>
@@ -7652,11 +7650,11 @@
       </c>
       <c r="N7" s="4">
         <f>M7*K7</f>
-        <v>136003.57139</v>
+        <v>517500</v>
       </c>
       <c r="O7" s="4">
         <f>N7-M7</f>
-        <v>135503.57139</v>
+        <v>517000</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>681</v>
@@ -7672,11 +7670,11 @@
       <c r="A8" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>44</v>
+      <c r="B8" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="C8" s="3">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>685</v>
@@ -7688,10 +7686,10 @@
         <v>680</v>
       </c>
       <c r="G8" s="4">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="H8" s="4">
-        <v>69</v>
+        <v>2116.5</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="8">
@@ -7699,11 +7697,11 @@
       </c>
       <c r="K8" s="4">
         <f>IF(ISNUMBER(I8),I8,IF(AND(ISNUMBER(G8),ISNUMBER(H8)),H8/G8,NA()))*J8</f>
-        <v>69</v>
+        <v>564.4</v>
       </c>
       <c r="L8" s="8">
         <f>K8-1</f>
-        <v>68</v>
+        <v>563.4</v>
       </c>
       <c r="M8" s="4">
         <f>$B$2</f>
@@ -7711,11 +7709,11 @@
       </c>
       <c r="N8" s="4">
         <f>M8*K8</f>
-        <v>34500</v>
+        <v>282200</v>
       </c>
       <c r="O8" s="4">
         <f>N8-M8</f>
-        <v>34000</v>
+        <v>281700</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>687</v>
@@ -7732,10 +7730,10 @@
         <v>690</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>389</v>
       </c>
       <c r="C9" s="3">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>691</v>
@@ -7744,13 +7742,13 @@
         <v>692</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="G9" s="4">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="H9" s="4">
-        <v>160</v>
+        <v>1748.04</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="8">
@@ -7758,11 +7756,11 @@
       </c>
       <c r="K9" s="4">
         <f>IF(ISNUMBER(I9),I9,IF(AND(ISNUMBER(G9),ISNUMBER(H9)),H9/G9,NA()))*J9</f>
-        <v>10.6666666666667</v>
+        <v>364.175</v>
       </c>
       <c r="L9" s="8">
         <f>K9-1</f>
-        <v>9.66666666666667</v>
+        <v>363.175</v>
       </c>
       <c r="M9" s="4">
         <f>$B$2</f>
@@ -7770,176 +7768,176 @@
       </c>
       <c r="N9" s="4">
         <f>M9*K9</f>
-        <v>5333.33333333333</v>
+        <v>182087.5</v>
       </c>
       <c r="O9" s="4">
         <f>N9-M9</f>
-        <v>4833.33333333333</v>
+        <v>181587.5</v>
       </c>
       <c r="P9" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="Q9" s="3" t="s">
+    </row>
+    <row r="10" ht="105" customHeight="1" spans="1:18">
+      <c r="A10" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2013</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="10" ht="105" customHeight="1" spans="1:18">
-      <c r="A10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2014</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G10" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="H10" s="10">
-        <v>90</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="11">
+      <c r="G10" s="4">
         <v>1</v>
       </c>
-      <c r="K10" s="6">
+      <c r="H10" s="4">
+        <v>272.00714278</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="8">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4">
         <f>IF(ISNUMBER(I10),I10,IF(AND(ISNUMBER(G10),ISNUMBER(H10)),H10/G10,NA()))*J10</f>
-        <v>36</v>
-      </c>
-      <c r="L10" s="11">
+        <v>272.00714278</v>
+      </c>
+      <c r="L10" s="8">
         <f>K10-1</f>
-        <v>35</v>
-      </c>
-      <c r="M10" s="6">
+        <v>271.00714278</v>
+      </c>
+      <c r="M10" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="4">
         <f>M10*K10</f>
-        <v>18000</v>
-      </c>
-      <c r="O10" s="6">
+        <v>136003.57139</v>
+      </c>
+      <c r="O10" s="4">
         <f>N10-M10</f>
-        <v>17500</v>
-      </c>
-      <c r="P10" s="5" t="s">
+        <v>135503.57139</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="Q10" s="5" t="s">
+      <c r="R10" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="R10" s="5" t="s">
+    </row>
+    <row r="11" ht="105" customHeight="1" spans="1:18">
+      <c r="A11" s="5" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="11" ht="105" customHeight="1" spans="1:18">
-      <c r="A11" s="3" t="s">
+      <c r="B11" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2015</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="6">
+        <v>2.2</v>
+      </c>
+      <c r="H11" s="6">
+        <v>500</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10">
         <v>1</v>
       </c>
-      <c r="H11" s="4">
-        <v>111.35738</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="8">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4">
+      <c r="K11" s="6">
         <f>IF(ISNUMBER(I11),I11,IF(AND(ISNUMBER(G11),ISNUMBER(H11)),H11/G11,NA()))*J11</f>
-        <v>111.35738</v>
-      </c>
-      <c r="L11" s="8">
+        <v>227.272727272727</v>
+      </c>
+      <c r="L11" s="10">
         <f>K11-1</f>
-        <v>110.35738</v>
-      </c>
-      <c r="M11" s="4">
+        <v>226.272727272727</v>
+      </c>
+      <c r="M11" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="6">
         <f>M11*K11</f>
-        <v>55678.69</v>
-      </c>
-      <c r="O11" s="4">
+        <v>113636.363636364</v>
+      </c>
+      <c r="O11" s="6">
         <f>N11-M11</f>
-        <v>55178.69</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="R11" s="3" t="s">
+        <v>113136.363636364</v>
+      </c>
+      <c r="P11" s="5" t="s">
         <v>704</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="12" ht="105" customHeight="1" spans="1:18">
       <c r="A12" s="5" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>81</v>
+        <v>502</v>
       </c>
       <c r="C12" s="5">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="G12" s="6">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H12" s="6">
-        <v>62.136442</v>
+        <v>500</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <v>1</v>
       </c>
       <c r="K12" s="6">
         <f>IF(ISNUMBER(I12),I12,IF(AND(ISNUMBER(G12),ISNUMBER(H12)),H12/G12,NA()))*J12</f>
-        <v>41.4242946666667</v>
-      </c>
-      <c r="L12" s="11">
+        <v>166.666666666667</v>
+      </c>
+      <c r="L12" s="10">
         <f>K12-1</f>
-        <v>40.4242946666667</v>
+        <v>165.666666666667</v>
       </c>
       <c r="M12" s="6">
         <f>$B$2</f>
@@ -7947,58 +7945,58 @@
       </c>
       <c r="N12" s="6">
         <f>M12*K12</f>
-        <v>20712.1473333333</v>
+        <v>83333.3333333333</v>
       </c>
       <c r="O12" s="6">
         <f>N12-M12</f>
-        <v>20212.1473333333</v>
+        <v>82833.3333333333</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="13" ht="105" customHeight="1" spans="1:18">
       <c r="A13" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>148</v>
+        <v>714</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>539</v>
       </c>
       <c r="C13" s="5">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>686</v>
-      </c>
-      <c r="F13" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>680</v>
       </c>
       <c r="G13" s="6">
         <v>1</v>
       </c>
       <c r="H13" s="6">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="I13" s="6"/>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <v>1</v>
       </c>
       <c r="K13" s="6">
         <f>IF(ISNUMBER(I13),I13,IF(AND(ISNUMBER(G13),ISNUMBER(H13)),H13/G13,NA()))*J13</f>
-        <v>40</v>
-      </c>
-      <c r="L13" s="11">
+        <v>130</v>
+      </c>
+      <c r="L13" s="10">
         <f>K13-1</f>
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="M13" s="6">
         <f>$B$2</f>
@@ -8006,105 +8004,105 @@
       </c>
       <c r="N13" s="6">
         <f>M13*K13</f>
-        <v>20000</v>
+        <v>65000</v>
       </c>
       <c r="O13" s="6">
         <f>N13-M13</f>
-        <v>19500</v>
+        <v>64500</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>687</v>
+        <v>717</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="14" ht="105" customHeight="1" spans="1:18">
-      <c r="A14" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="A14" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="3">
         <v>2015</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>715</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="D14" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G14" s="6">
-        <v>33.2592</v>
-      </c>
-      <c r="H14" s="6">
-        <v>518.49</v>
-      </c>
-      <c r="I14" s="6"/>
-      <c r="J14" s="11">
+      <c r="G14" s="4">
         <v>1</v>
       </c>
-      <c r="K14" s="6">
+      <c r="H14" s="4">
+        <v>111.35738</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="8">
+        <v>1</v>
+      </c>
+      <c r="K14" s="4">
         <f>IF(ISNUMBER(I14),I14,IF(AND(ISNUMBER(G14),ISNUMBER(H14)),H14/G14,NA()))*J14</f>
-        <v>15.5893707605715</v>
-      </c>
-      <c r="L14" s="11">
+        <v>111.35738</v>
+      </c>
+      <c r="L14" s="8">
         <f>K14-1</f>
-        <v>14.5893707605715</v>
-      </c>
-      <c r="M14" s="6">
+        <v>110.35738</v>
+      </c>
+      <c r="M14" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="4">
         <f>M14*K14</f>
-        <v>7794.68538028576</v>
-      </c>
-      <c r="O14" s="6">
+        <v>55678.69</v>
+      </c>
+      <c r="O14" s="4">
         <f>N14-M14</f>
-        <v>7294.68538028576</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>718</v>
+        <v>55178.69</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="15" ht="105" customHeight="1" spans="1:18">
       <c r="A15" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>629</v>
+        <v>724</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>250</v>
       </c>
       <c r="C15" s="3">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>680</v>
       </c>
       <c r="G15" s="4">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H15" s="4">
-        <v>290.1402496496</v>
+        <v>207</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="8">
@@ -8112,11 +8110,11 @@
       </c>
       <c r="K15" s="4">
         <f>IF(ISNUMBER(I15),I15,IF(AND(ISNUMBER(G15),ISNUMBER(H15)),H15/G15,NA()))*J15</f>
-        <v>4.3960643886303</v>
+        <v>103.5</v>
       </c>
       <c r="L15" s="8">
         <f>K15-1</f>
-        <v>3.3960643886303</v>
+        <v>102.5</v>
       </c>
       <c r="M15" s="4">
         <f>$B$2</f>
@@ -8124,113 +8122,117 @@
       </c>
       <c r="N15" s="4">
         <f>M15*K15</f>
-        <v>2198.03219431515</v>
+        <v>51750</v>
       </c>
       <c r="O15" s="4">
         <f>N15-M15</f>
-        <v>1698.03219431515</v>
+        <v>51250</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="16" ht="105" customHeight="1" spans="1:18">
-      <c r="A16" s="5" t="s">
-        <v>724</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2015</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="A16" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="J16" s="11">
+      <c r="G16" s="4">
+        <v>16.46</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1668.6</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="8">
         <v>1</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="4">
         <f>IF(ISNUMBER(I16),I16,IF(AND(ISNUMBER(G16),ISNUMBER(H16)),H16/G16,NA()))*J16</f>
-        <v>0.1</v>
-      </c>
-      <c r="L16" s="11">
+        <v>101.373025516403</v>
+      </c>
+      <c r="L16" s="8">
         <f>K16-1</f>
-        <v>-0.9</v>
-      </c>
-      <c r="M16" s="6">
+        <v>100.373025516403</v>
+      </c>
+      <c r="M16" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="4">
         <f>M16*K16</f>
-        <v>50</v>
-      </c>
-      <c r="O16" s="6">
+        <v>50686.5127582017</v>
+      </c>
+      <c r="O16" s="4">
         <f>N16-M16</f>
-        <v>-450</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>727</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>728</v>
+        <v>50186.5127582017</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="17" ht="105" customHeight="1" spans="1:18">
       <c r="A17" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>160</v>
+        <v>732</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="C17" s="3">
         <v>2016</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4">
-        <v>1035</v>
-      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <v>100</v>
+      </c>
+      <c r="I17" s="4"/>
       <c r="J17" s="8">
         <v>1</v>
       </c>
       <c r="K17" s="4">
         <f>IF(ISNUMBER(I17),I17,IF(AND(ISNUMBER(G17),ISNUMBER(H17)),H17/G17,NA()))*J17</f>
-        <v>1035</v>
+        <v>100</v>
       </c>
       <c r="L17" s="8">
         <f>K17-1</f>
-        <v>1034</v>
+        <v>99</v>
       </c>
       <c r="M17" s="4">
         <f>$B$2</f>
@@ -8238,46 +8240,46 @@
       </c>
       <c r="N17" s="4">
         <f>M17*K17</f>
-        <v>517500</v>
+        <v>50000</v>
       </c>
       <c r="O17" s="4">
         <f>N17-M17</f>
-        <v>517000</v>
+        <v>49500</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="18" ht="105" customHeight="1" spans="1:18">
       <c r="A18" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>250</v>
+        <v>737</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>415</v>
       </c>
       <c r="C18" s="3">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>698</v>
+        <v>738</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>680</v>
       </c>
       <c r="G18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="4">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="8">
@@ -8285,11 +8287,11 @@
       </c>
       <c r="K18" s="4">
         <f>IF(ISNUMBER(I18),I18,IF(AND(ISNUMBER(G18),ISNUMBER(H18)),H18/G18,NA()))*J18</f>
-        <v>103.5</v>
+        <v>100</v>
       </c>
       <c r="L18" s="8">
         <f>K18-1</f>
-        <v>102.5</v>
+        <v>99</v>
       </c>
       <c r="M18" s="4">
         <f>$B$2</f>
@@ -8297,37 +8299,37 @@
       </c>
       <c r="N18" s="4">
         <f>M18*K18</f>
-        <v>51750</v>
+        <v>50000</v>
       </c>
       <c r="O18" s="4">
         <f>N18-M18</f>
-        <v>51250</v>
+        <v>49500</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>699</v>
+        <v>740</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:18">
       <c r="A19" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>198</v>
+        <v>743</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>478</v>
       </c>
       <c r="C19" s="3">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>680</v>
@@ -8363,51 +8365,51 @@
         <v>49500</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>687</v>
+        <v>746</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="20" ht="105" customHeight="1" spans="1:18">
       <c r="A20" s="5" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>186</v>
+        <v>577</v>
       </c>
       <c r="C20" s="5">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>698</v>
+        <v>750</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>692</v>
+        <v>751</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>680</v>
       </c>
       <c r="G20" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="6">
         <v>100</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <v>1</v>
       </c>
       <c r="K20" s="6">
         <f>IF(ISNUMBER(I20),I20,IF(AND(ISNUMBER(G20),ISNUMBER(H20)),H20/G20,NA()))*J20</f>
-        <v>33.3333333333333</v>
-      </c>
-      <c r="L20" s="11">
+        <v>100</v>
+      </c>
+      <c r="L20" s="10">
         <f>K20-1</f>
-        <v>32.3333333333333</v>
+        <v>99</v>
       </c>
       <c r="M20" s="6">
         <f>$B$2</f>
@@ -8415,117 +8417,115 @@
       </c>
       <c r="N20" s="6">
         <f>M20*K20</f>
-        <v>16666.6666666667</v>
+        <v>50000</v>
       </c>
       <c r="O20" s="6">
         <f>N20-M20</f>
-        <v>16166.6666666667</v>
+        <v>49500</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="Q20" s="5" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
     </row>
     <row r="21" ht="105" customHeight="1" spans="1:18">
-      <c r="A21" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="3">
-        <v>2016</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="A21" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2017</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G21" s="4">
-        <v>2.1</v>
-      </c>
-      <c r="H21" s="4">
-        <v>65.753668</v>
-      </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="8">
+      <c r="G21" s="6">
+        <v>66.3</v>
+      </c>
+      <c r="H21" s="6">
+        <v>5641.89</v>
+      </c>
+      <c r="I21" s="6"/>
+      <c r="J21" s="10">
         <v>1</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="6">
         <f>IF(ISNUMBER(I21),I21,IF(AND(ISNUMBER(G21),ISNUMBER(H21)),H21/G21,NA()))*J21</f>
-        <v>31.3112704761905</v>
-      </c>
-      <c r="L21" s="8">
+        <v>85.0963800904977</v>
+      </c>
+      <c r="L21" s="10">
         <f>K21-1</f>
-        <v>30.3112704761905</v>
-      </c>
-      <c r="M21" s="4">
+        <v>84.0963800904977</v>
+      </c>
+      <c r="M21" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N21" s="4">
+      <c r="N21" s="6">
         <f>M21*K21</f>
-        <v>15655.6352380952</v>
-      </c>
-      <c r="O21" s="4">
+        <v>42548.1900452489</v>
+      </c>
+      <c r="O21" s="6">
         <f>N21-M21</f>
-        <v>15155.6352380952</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>750</v>
+        <v>42048.1900452489</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q21" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="R21" s="5" t="s">
+        <v>759</v>
       </c>
     </row>
     <row r="22" ht="105" customHeight="1" spans="1:18">
       <c r="A22" s="5" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>224</v>
+        <v>551</v>
       </c>
       <c r="C22" s="5">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G22" s="6">
-        <v>15</v>
-      </c>
-      <c r="H22" s="6">
-        <v>428.9924925</v>
-      </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="11">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6">
+        <v>80</v>
+      </c>
+      <c r="J22" s="10">
         <v>1</v>
       </c>
       <c r="K22" s="6">
         <f>IF(ISNUMBER(I22),I22,IF(AND(ISNUMBER(G22),ISNUMBER(H22)),H22/G22,NA()))*J22</f>
-        <v>28.5994995</v>
-      </c>
-      <c r="L22" s="11">
+        <v>80</v>
+      </c>
+      <c r="L22" s="10">
         <f>K22-1</f>
-        <v>27.5994995</v>
+        <v>79</v>
       </c>
       <c r="M22" s="6">
         <f>$B$2</f>
@@ -8533,46 +8533,46 @@
       </c>
       <c r="N22" s="6">
         <f>M22*K22</f>
-        <v>14299.74975</v>
+        <v>40000</v>
       </c>
       <c r="O22" s="6">
         <f>N22-M22</f>
-        <v>13799.74975</v>
+        <v>39500</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
     </row>
     <row r="23" ht="105" customHeight="1" spans="1:18">
       <c r="A23" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>212</v>
+        <v>762</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="C23" s="3">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="F23" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>680</v>
       </c>
       <c r="G23" s="4">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="H23" s="4">
-        <v>146</v>
+        <v>69</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="8">
@@ -8580,11 +8580,11 @@
       </c>
       <c r="K23" s="4">
         <f>IF(ISNUMBER(I23),I23,IF(AND(ISNUMBER(G23),ISNUMBER(H23)),H23/G23,NA()))*J23</f>
-        <v>26.5454545454545</v>
+        <v>69</v>
       </c>
       <c r="L23" s="8">
         <f>K23-1</f>
-        <v>25.5454545454545</v>
+        <v>68</v>
       </c>
       <c r="M23" s="4">
         <f>$B$2</f>
@@ -8592,58 +8592,56 @@
       </c>
       <c r="N23" s="4">
         <f>M23*K23</f>
-        <v>13272.7272727273</v>
+        <v>34500</v>
       </c>
       <c r="O23" s="4">
         <f>N23-M23</f>
-        <v>12772.7272727273</v>
+        <v>34000</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>759</v>
+        <v>681</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
     </row>
     <row r="24" ht="105" customHeight="1" spans="1:18">
       <c r="A24" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>94</v>
+        <v>590</v>
       </c>
       <c r="C24" s="3">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>764</v>
+        <v>679</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G24" s="4">
-        <v>14.82</v>
-      </c>
-      <c r="H24" s="4">
-        <v>267.614377</v>
-      </c>
-      <c r="I24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4">
+        <v>60</v>
+      </c>
       <c r="J24" s="8">
         <v>1</v>
       </c>
       <c r="K24" s="4">
         <f>IF(ISNUMBER(I24),I24,IF(AND(ISNUMBER(G24),ISNUMBER(H24)),H24/G24,NA()))*J24</f>
-        <v>18.0576502699055</v>
+        <v>60</v>
       </c>
       <c r="L24" s="8">
         <f>K24-1</f>
-        <v>17.0576502699055</v>
+        <v>59</v>
       </c>
       <c r="M24" s="4">
         <f>$B$2</f>
@@ -8651,58 +8649,58 @@
       </c>
       <c r="N24" s="4">
         <f>M24*K24</f>
-        <v>9028.82513495277</v>
+        <v>30000</v>
       </c>
       <c r="O24" s="4">
         <f>N24-M24</f>
-        <v>8528.82513495277</v>
+        <v>29500</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>766</v>
+        <v>683</v>
       </c>
     </row>
     <row r="25" ht="105" customHeight="1" spans="1:18">
       <c r="A25" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>263</v>
+        <v>770</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>300</v>
       </c>
       <c r="C25" s="5">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>680</v>
       </c>
       <c r="G25" s="6">
-        <v>66.3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="6">
-        <v>5641.89</v>
+        <v>110</v>
       </c>
       <c r="I25" s="6"/>
-      <c r="J25" s="11">
+      <c r="J25" s="10">
         <v>1</v>
       </c>
       <c r="K25" s="6">
         <f>IF(ISNUMBER(I25),I25,IF(AND(ISNUMBER(G25),ISNUMBER(H25)),H25/G25,NA()))*J25</f>
-        <v>85.0963800904977</v>
-      </c>
-      <c r="L25" s="11">
+        <v>55</v>
+      </c>
+      <c r="L25" s="10">
         <f>K25-1</f>
-        <v>84.0963800904977</v>
+        <v>54</v>
       </c>
       <c r="M25" s="6">
         <f>$B$2</f>
@@ -8710,117 +8708,117 @@
       </c>
       <c r="N25" s="6">
         <f>M25*K25</f>
-        <v>42548.1900452489</v>
+        <v>27500</v>
       </c>
       <c r="O25" s="6">
         <f>N25-M25</f>
-        <v>42048.1900452489</v>
+        <v>27000</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>699</v>
+        <v>773</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="R25" s="5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
     </row>
     <row r="26" ht="105" customHeight="1" spans="1:18">
-      <c r="A26" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="C26" s="3">
-        <v>2017</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="A26" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C26" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="6">
+        <v>4</v>
+      </c>
+      <c r="H26" s="6">
+        <v>200</v>
+      </c>
+      <c r="I26" s="6"/>
+      <c r="J26" s="10">
         <v>1</v>
       </c>
-      <c r="H26" s="4">
-        <v>40</v>
-      </c>
-      <c r="I26" s="4"/>
-      <c r="J26" s="8">
-        <v>1</v>
-      </c>
-      <c r="K26" s="4">
+      <c r="K26" s="6">
         <f>IF(ISNUMBER(I26),I26,IF(AND(ISNUMBER(G26),ISNUMBER(H26)),H26/G26,NA()))*J26</f>
-        <v>40</v>
-      </c>
-      <c r="L26" s="8">
+        <v>50</v>
+      </c>
+      <c r="L26" s="10">
         <f>K26-1</f>
-        <v>39</v>
-      </c>
-      <c r="M26" s="4">
+        <v>49</v>
+      </c>
+      <c r="M26" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="6">
         <f>M26*K26</f>
-        <v>20000</v>
-      </c>
-      <c r="O26" s="4">
+        <v>25000</v>
+      </c>
+      <c r="O26" s="6">
         <f>N26-M26</f>
-        <v>19500</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>776</v>
+        <v>24500</v>
+      </c>
+      <c r="P26" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="R26" s="5" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="27" ht="105" customHeight="1" spans="1:18">
       <c r="A27" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>300</v>
+        <v>782</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>515</v>
       </c>
       <c r="C27" s="5">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>680</v>
       </c>
       <c r="G27" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="6">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="I27" s="6"/>
-      <c r="J27" s="11">
+      <c r="J27" s="10">
         <v>1</v>
       </c>
       <c r="K27" s="6">
         <f>IF(ISNUMBER(I27),I27,IF(AND(ISNUMBER(G27),ISNUMBER(H27)),H27/G27,NA()))*J27</f>
-        <v>55</v>
-      </c>
-      <c r="L27" s="11">
+        <v>50</v>
+      </c>
+      <c r="L27" s="10">
         <f>K27-1</f>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M27" s="6">
         <f>$B$2</f>
@@ -8828,115 +8826,117 @@
       </c>
       <c r="N27" s="6">
         <f>M27*K27</f>
-        <v>27500</v>
+        <v>25000</v>
       </c>
       <c r="O27" s="6">
         <f>N27-M27</f>
-        <v>27000</v>
+        <v>24500</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
     </row>
     <row r="28" ht="105" customHeight="1" spans="1:18">
-      <c r="A28" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C28" s="3">
-        <v>2018</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="G28" s="4">
-        <v>3</v>
-      </c>
-      <c r="H28" s="4">
-        <v>48</v>
-      </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="8">
+      <c r="A28" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="5">
+        <v>2015</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="G28" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="H28" s="6">
+        <v>62.136442</v>
+      </c>
+      <c r="I28" s="6"/>
+      <c r="J28" s="10">
         <v>1</v>
       </c>
-      <c r="K28" s="4">
+      <c r="K28" s="6">
         <f>IF(ISNUMBER(I28),I28,IF(AND(ISNUMBER(G28),ISNUMBER(H28)),H28/G28,NA()))*J28</f>
-        <v>16</v>
-      </c>
-      <c r="L28" s="8">
+        <v>41.4242946666667</v>
+      </c>
+      <c r="L28" s="10">
         <f>K28-1</f>
-        <v>15</v>
-      </c>
-      <c r="M28" s="4">
+        <v>40.4242946666667</v>
+      </c>
+      <c r="M28" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N28" s="4">
+      <c r="N28" s="6">
         <f>M28*K28</f>
-        <v>8000</v>
-      </c>
-      <c r="O28" s="4">
+        <v>20712.1473333333</v>
+      </c>
+      <c r="O28" s="6">
         <f>N28-M28</f>
-        <v>7500</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>787</v>
+        <v>20212.1473333333</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="R28" s="5" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="29" ht="105" customHeight="1" spans="1:18">
       <c r="A29" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>288</v>
+        <v>792</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>148</v>
       </c>
       <c r="C29" s="5">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>790</v>
+        <v>764</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="J29" s="11">
+      <c r="G29" s="6">
+        <v>1</v>
+      </c>
+      <c r="H29" s="6">
+        <v>40</v>
+      </c>
+      <c r="I29" s="6"/>
+      <c r="J29" s="10">
         <v>1</v>
       </c>
       <c r="K29" s="6">
         <f>IF(ISNUMBER(I29),I29,IF(AND(ISNUMBER(G29),ISNUMBER(H29)),H29/G29,NA()))*J29</f>
-        <v>0.1</v>
-      </c>
-      <c r="L29" s="11">
+        <v>40</v>
+      </c>
+      <c r="L29" s="10">
         <f>K29-1</f>
-        <v>-0.9</v>
+        <v>39</v>
       </c>
       <c r="M29" s="6">
         <f>$B$2</f>
@@ -8944,46 +8944,46 @@
       </c>
       <c r="N29" s="6">
         <f>M29*K29</f>
-        <v>50</v>
+        <v>20000</v>
       </c>
       <c r="O29" s="6">
         <f>N29-M29</f>
-        <v>-450</v>
+        <v>19500</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="Q29" s="5" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="30" ht="105" customHeight="1" spans="1:18">
       <c r="A30" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>312</v>
+        <v>796</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>276</v>
       </c>
       <c r="C30" s="3">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>680</v>
       </c>
       <c r="G30" s="4">
-        <v>3.75</v>
+        <v>1</v>
       </c>
       <c r="H30" s="4">
-        <v>2116.5</v>
+        <v>40</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="8">
@@ -8991,11 +8991,11 @@
       </c>
       <c r="K30" s="4">
         <f>IF(ISNUMBER(I30),I30,IF(AND(ISNUMBER(G30),ISNUMBER(H30)),H30/G30,NA()))*J30</f>
-        <v>564.4</v>
+        <v>40</v>
       </c>
       <c r="L30" s="8">
         <f>K30-1</f>
-        <v>563.4</v>
+        <v>39</v>
       </c>
       <c r="M30" s="4">
         <f>$B$2</f>
@@ -9003,196 +9003,196 @@
       </c>
       <c r="N30" s="4">
         <f>M30*K30</f>
-        <v>282200</v>
+        <v>20000</v>
       </c>
       <c r="O30" s="4">
         <f>N30-M30</f>
-        <v>281700</v>
+        <v>19500</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="31" ht="105" customHeight="1" spans="1:18">
-      <c r="A31" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C31" s="3">
-        <v>2019</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="G31" s="4">
+      <c r="A31" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2022</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>734</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="G31" s="6">
+        <v>2</v>
+      </c>
+      <c r="H31" s="6">
+        <v>80</v>
+      </c>
+      <c r="I31" s="6"/>
+      <c r="J31" s="10">
         <v>1</v>
       </c>
-      <c r="H31" s="4">
-        <v>16.7</v>
-      </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="8">
-        <v>1</v>
-      </c>
-      <c r="K31" s="4">
+      <c r="K31" s="6">
         <f>IF(ISNUMBER(I31),I31,IF(AND(ISNUMBER(G31),ISNUMBER(H31)),H31/G31,NA()))*J31</f>
-        <v>16.7</v>
-      </c>
-      <c r="L31" s="8">
+        <v>40</v>
+      </c>
+      <c r="L31" s="10">
         <f>K31-1</f>
-        <v>15.7</v>
-      </c>
-      <c r="M31" s="4">
+        <v>39</v>
+      </c>
+      <c r="M31" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N31" s="4">
+      <c r="N31" s="6">
         <f>M31*K31</f>
-        <v>8350</v>
-      </c>
-      <c r="O31" s="4">
+        <v>20000</v>
+      </c>
+      <c r="O31" s="6">
         <f>N31-M31</f>
-        <v>7850</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="Q31" s="3" t="s">
+        <v>19500</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q31" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="R31" s="3" t="s">
+      <c r="R31" s="5" t="s">
         <v>803</v>
       </c>
     </row>
     <row r="32" ht="105" customHeight="1" spans="1:18">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C32" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="5">
+        <v>2014</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G32" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="H32" s="4">
-        <v>1748.04</v>
-      </c>
-      <c r="I32" s="4"/>
-      <c r="J32" s="8">
+      <c r="G32" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="H32" s="9">
+        <v>90</v>
+      </c>
+      <c r="I32" s="6"/>
+      <c r="J32" s="10">
         <v>1</v>
       </c>
-      <c r="K32" s="4">
+      <c r="K32" s="6">
         <f>IF(ISNUMBER(I32),I32,IF(AND(ISNUMBER(G32),ISNUMBER(H32)),H32/G32,NA()))*J32</f>
-        <v>364.175</v>
-      </c>
-      <c r="L32" s="8">
+        <v>36</v>
+      </c>
+      <c r="L32" s="10">
         <f>K32-1</f>
-        <v>363.175</v>
-      </c>
-      <c r="M32" s="4">
+        <v>35</v>
+      </c>
+      <c r="M32" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N32" s="4">
+      <c r="N32" s="6">
         <f>M32*K32</f>
-        <v>182087.5</v>
-      </c>
-      <c r="O32" s="4">
+        <v>18000</v>
+      </c>
+      <c r="O32" s="6">
         <f>N32-M32</f>
-        <v>181587.5</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q32" s="3" t="s">
+        <v>17500</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="33" ht="105" customHeight="1" spans="1:18">
+      <c r="A33" s="5" t="s">
         <v>807</v>
       </c>
-      <c r="R32" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C33" s="5">
+        <v>2022</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="33" ht="105" customHeight="1" spans="1:18">
-      <c r="A33" s="3" t="s">
+      <c r="E33" s="5" t="s">
         <v>809</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="C33" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G33" s="4">
-        <v>16.46</v>
-      </c>
-      <c r="H33" s="4">
-        <v>1668.6</v>
-      </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="8">
+      <c r="G33" s="6">
+        <v>15</v>
+      </c>
+      <c r="H33" s="6">
+        <v>539</v>
+      </c>
+      <c r="I33" s="6"/>
+      <c r="J33" s="10">
         <v>1</v>
       </c>
-      <c r="K33" s="4">
+      <c r="K33" s="6">
         <f>IF(ISNUMBER(I33),I33,IF(AND(ISNUMBER(G33),ISNUMBER(H33)),H33/G33,NA()))*J33</f>
-        <v>101.373025516403</v>
-      </c>
-      <c r="L33" s="8">
+        <v>35.9333333333333</v>
+      </c>
+      <c r="L33" s="10">
         <f>K33-1</f>
-        <v>100.373025516403</v>
-      </c>
-      <c r="M33" s="4">
+        <v>34.9333333333333</v>
+      </c>
+      <c r="M33" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N33" s="4">
+      <c r="N33" s="6">
         <f>M33*K33</f>
-        <v>50686.5127582017</v>
-      </c>
-      <c r="O33" s="4">
+        <v>17966.6666666667</v>
+      </c>
+      <c r="O33" s="6">
         <f>N33-M33</f>
-        <v>50186.5127582017</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q33" s="3" t="s">
+        <v>17466.6666666667</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q33" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="R33" s="3" t="s">
+      <c r="R33" s="5" t="s">
         <v>812</v>
       </c>
     </row>
@@ -9201,37 +9201,37 @@
         <v>813</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>376</v>
+        <v>186</v>
       </c>
       <c r="C34" s="5">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>739</v>
+        <v>702</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>680</v>
       </c>
       <c r="G34" s="6">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="H34" s="6">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="I34" s="6"/>
-      <c r="J34" s="11">
+      <c r="J34" s="10">
         <v>1</v>
       </c>
       <c r="K34" s="6">
         <f>IF(ISNUMBER(I34),I34,IF(AND(ISNUMBER(G34),ISNUMBER(H34)),H34/G34,NA()))*J34</f>
-        <v>20</v>
-      </c>
-      <c r="L34" s="11">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="L34" s="10">
         <f>K34-1</f>
-        <v>19</v>
+        <v>32.3333333333333</v>
       </c>
       <c r="M34" s="6">
         <f>$B$2</f>
@@ -9239,46 +9239,46 @@
       </c>
       <c r="N34" s="6">
         <f>M34*K34</f>
-        <v>10000</v>
+        <v>16666.6666666667</v>
       </c>
       <c r="O34" s="6">
         <f>N34-M34</f>
-        <v>9500</v>
+        <v>16166.6666666667</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>687</v>
+        <v>814</v>
       </c>
       <c r="Q34" s="5" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="R34" s="5" t="s">
-        <v>742</v>
+        <v>816</v>
       </c>
     </row>
     <row r="35" ht="105" customHeight="1" spans="1:18">
       <c r="A35" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>817</v>
+        <v>789</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>680</v>
       </c>
       <c r="G35" s="4">
-        <v>1565</v>
+        <v>2.1</v>
       </c>
       <c r="H35" s="4">
-        <v>29590.68</v>
+        <v>65.753668</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="8">
@@ -9286,11 +9286,11 @@
       </c>
       <c r="K35" s="4">
         <f>IF(ISNUMBER(I35),I35,IF(AND(ISNUMBER(G35),ISNUMBER(H35)),H35/G35,NA()))*J35</f>
-        <v>18.9077827476038</v>
+        <v>31.3112704761905</v>
       </c>
       <c r="L35" s="8">
         <f>K35-1</f>
-        <v>17.9077827476038</v>
+        <v>30.3112704761905</v>
       </c>
       <c r="M35" s="4">
         <f>$B$2</f>
@@ -9298,115 +9298,117 @@
       </c>
       <c r="N35" s="4">
         <f>M35*K35</f>
-        <v>9453.89137380192</v>
+        <v>15655.6352380952</v>
       </c>
       <c r="O35" s="4">
         <f>N35-M35</f>
-        <v>8953.89137380192</v>
+        <v>15155.6352380952</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="36" ht="105" customHeight="1" spans="1:18">
-      <c r="A36" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C36" s="3">
-        <v>2020</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>821</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2016</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>822</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G36" s="4">
-        <v>29.08</v>
-      </c>
-      <c r="H36" s="4">
-        <v>228.75</v>
-      </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="8">
+      <c r="G36" s="6">
+        <v>15</v>
+      </c>
+      <c r="H36" s="6">
+        <v>428.9924925</v>
+      </c>
+      <c r="I36" s="6"/>
+      <c r="J36" s="10">
         <v>1</v>
       </c>
-      <c r="K36" s="4">
+      <c r="K36" s="6">
         <f>IF(ISNUMBER(I36),I36,IF(AND(ISNUMBER(G36),ISNUMBER(H36)),H36/G36,NA()))*J36</f>
-        <v>7.8662310866575</v>
-      </c>
-      <c r="L36" s="8">
+        <v>28.5994995</v>
+      </c>
+      <c r="L36" s="10">
         <f>K36-1</f>
-        <v>6.8662310866575</v>
-      </c>
-      <c r="M36" s="4">
+        <v>27.5994995</v>
+      </c>
+      <c r="M36" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="6">
         <f>M36*K36</f>
-        <v>3933.11554332875</v>
-      </c>
-      <c r="O36" s="4">
+        <v>14299.74975</v>
+      </c>
+      <c r="O36" s="6">
         <f>N36-M36</f>
-        <v>3433.11554332875</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="R36" s="3" t="s">
+        <v>13799.74975</v>
+      </c>
+      <c r="P36" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q36" s="5" t="s">
         <v>824</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="37" ht="105" customHeight="1" spans="1:18">
       <c r="A37" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>353</v>
+        <v>603</v>
       </c>
       <c r="C37" s="3">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>789</v>
+        <v>827</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>790</v>
+        <v>828</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4">
-        <v>0.1</v>
-      </c>
+      <c r="G37" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="H37" s="4">
+        <v>77.4</v>
+      </c>
+      <c r="I37" s="4"/>
       <c r="J37" s="8">
         <v>1</v>
       </c>
       <c r="K37" s="4">
         <f>IF(ISNUMBER(I37),I37,IF(AND(ISNUMBER(G37),ISNUMBER(H37)),H37/G37,NA()))*J37</f>
-        <v>0.1</v>
+        <v>27.6428571428571</v>
       </c>
       <c r="L37" s="8">
         <f>K37-1</f>
-        <v>-0.9</v>
+        <v>26.6428571428571</v>
       </c>
       <c r="M37" s="4">
         <f>$B$2</f>
@@ -9414,172 +9416,176 @@
       </c>
       <c r="N37" s="4">
         <f>M37*K37</f>
-        <v>50</v>
+        <v>13821.4285714286</v>
       </c>
       <c r="O37" s="4">
         <f>N37-M37</f>
-        <v>-450</v>
+        <v>13321.4285714286</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>699</v>
+        <v>829</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
     </row>
     <row r="38" ht="105" customHeight="1" spans="1:18">
-      <c r="A38" s="5" t="s">
-        <v>827</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C38" s="5">
-        <v>2020</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>828</v>
+      <c r="A38" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2016</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>834</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="J38" s="11">
+      <c r="G38" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="H38" s="4">
+        <v>146</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="8">
         <v>1</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="4">
         <f>IF(ISNUMBER(I38),I38,IF(AND(ISNUMBER(G38),ISNUMBER(H38)),H38/G38,NA()))*J38</f>
-        <v>0.1</v>
-      </c>
-      <c r="L38" s="11">
+        <v>26.5454545454545</v>
+      </c>
+      <c r="L38" s="8">
         <f>K38-1</f>
-        <v>-0.9</v>
-      </c>
-      <c r="M38" s="6">
+        <v>25.5454545454545</v>
+      </c>
+      <c r="M38" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N38" s="6">
+      <c r="N38" s="4">
         <f>M38*K38</f>
-        <v>50</v>
-      </c>
-      <c r="O38" s="6">
+        <v>13272.7272727273</v>
+      </c>
+      <c r="O38" s="4">
         <f>N38-M38</f>
-        <v>-450</v>
-      </c>
-      <c r="P38" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>829</v>
-      </c>
-      <c r="R38" s="5" t="s">
-        <v>830</v>
+        <v>12772.7272727273</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="39" ht="105" customHeight="1" spans="1:18">
-      <c r="A39" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C39" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="A39" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="C39" s="5">
+        <v>2023</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="6">
+        <v>6</v>
+      </c>
+      <c r="H39" s="6">
+        <v>143</v>
+      </c>
+      <c r="I39" s="6"/>
+      <c r="J39" s="10">
         <v>1</v>
       </c>
-      <c r="H39" s="4">
-        <v>100</v>
-      </c>
-      <c r="I39" s="4"/>
-      <c r="J39" s="8">
-        <v>1</v>
-      </c>
-      <c r="K39" s="4">
+      <c r="K39" s="6">
         <f>IF(ISNUMBER(I39),I39,IF(AND(ISNUMBER(G39),ISNUMBER(H39)),H39/G39,NA()))*J39</f>
-        <v>100</v>
-      </c>
-      <c r="L39" s="8">
+        <v>23.8333333333333</v>
+      </c>
+      <c r="L39" s="10">
         <f>K39-1</f>
-        <v>99</v>
-      </c>
-      <c r="M39" s="4">
+        <v>22.8333333333333</v>
+      </c>
+      <c r="M39" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N39" s="4">
+      <c r="N39" s="6">
         <f>M39*K39</f>
-        <v>50000</v>
-      </c>
-      <c r="O39" s="4">
+        <v>11916.6666666667</v>
+      </c>
+      <c r="O39" s="6">
         <f>N39-M39</f>
-        <v>49500</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>836</v>
+        <v>11416.6666666667</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="R39" s="5" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="40" ht="105" customHeight="1" spans="1:18">
       <c r="A40" s="5" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="C40" s="5">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>838</v>
+        <v>733</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>839</v>
+        <v>734</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="J40" s="11">
+      <c r="G40" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="H40" s="6">
+        <v>52</v>
+      </c>
+      <c r="I40" s="6"/>
+      <c r="J40" s="10">
         <v>1</v>
       </c>
       <c r="K40" s="6">
         <f>IF(ISNUMBER(I40),I40,IF(AND(ISNUMBER(G40),ISNUMBER(H40)),H40/G40,NA()))*J40</f>
-        <v>0.1</v>
-      </c>
-      <c r="L40" s="11">
+        <v>20</v>
+      </c>
+      <c r="L40" s="10">
         <f>K40-1</f>
-        <v>-0.9</v>
+        <v>19</v>
       </c>
       <c r="M40" s="6">
         <f>$B$2</f>
@@ -9587,58 +9593,58 @@
       </c>
       <c r="N40" s="6">
         <f>M40*K40</f>
-        <v>50</v>
+        <v>10000</v>
       </c>
       <c r="O40" s="6">
         <f>N40-M40</f>
-        <v>-450</v>
+        <v>9500</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="Q40" s="5" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="R40" s="5" t="s">
-        <v>841</v>
+        <v>736</v>
       </c>
     </row>
     <row r="41" ht="105" customHeight="1" spans="1:18">
       <c r="A41" s="5" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>440</v>
+        <v>565</v>
       </c>
       <c r="C41" s="5">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>739</v>
+        <v>845</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>740</v>
+        <v>846</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>680</v>
       </c>
       <c r="G41" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H41" s="6">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I41" s="6"/>
-      <c r="J41" s="11">
+      <c r="J41" s="10">
         <v>1</v>
       </c>
       <c r="K41" s="6">
         <f>IF(ISNUMBER(I41),I41,IF(AND(ISNUMBER(G41),ISNUMBER(H41)),H41/G41,NA()))*J41</f>
-        <v>40</v>
-      </c>
-      <c r="L41" s="11">
+        <v>20</v>
+      </c>
+      <c r="L41" s="10">
         <f>K41-1</f>
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="M41" s="6">
         <f>$B$2</f>
@@ -9646,644 +9652,642 @@
       </c>
       <c r="N41" s="6">
         <f>M41*K41</f>
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="O41" s="6">
         <f>N41-M41</f>
-        <v>19500</v>
+        <v>9500</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>687</v>
+        <v>847</v>
       </c>
       <c r="Q41" s="5" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="R41" s="5" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
     </row>
     <row r="42" ht="105" customHeight="1" spans="1:18">
-      <c r="A42" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="C42" s="5">
-        <v>2022</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>847</v>
+      <c r="A42" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>852</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G42" s="6">
-        <v>15</v>
-      </c>
-      <c r="H42" s="6">
-        <v>539</v>
-      </c>
-      <c r="I42" s="6"/>
-      <c r="J42" s="11">
+      <c r="G42" s="4">
+        <v>1565</v>
+      </c>
+      <c r="H42" s="4">
+        <v>29590.68</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="8">
         <v>1</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="4">
         <f>IF(ISNUMBER(I42),I42,IF(AND(ISNUMBER(G42),ISNUMBER(H42)),H42/G42,NA()))*J42</f>
-        <v>35.9333333333333</v>
-      </c>
-      <c r="L42" s="11">
+        <v>18.9077827476038</v>
+      </c>
+      <c r="L42" s="8">
         <f>K42-1</f>
-        <v>34.9333333333333</v>
-      </c>
-      <c r="M42" s="6">
+        <v>17.9077827476038</v>
+      </c>
+      <c r="M42" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N42" s="6">
+      <c r="N42" s="4">
         <f>M42*K42</f>
-        <v>17966.6666666667</v>
-      </c>
-      <c r="O42" s="6">
+        <v>9453.89137380192</v>
+      </c>
+      <c r="O42" s="4">
         <f>N42-M42</f>
-        <v>17466.6666666667</v>
-      </c>
-      <c r="P42" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="Q42" s="5" t="s">
-        <v>849</v>
-      </c>
-      <c r="R42" s="5" t="s">
-        <v>850</v>
+        <v>8953.89137380192</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="43" ht="105" customHeight="1" spans="1:18">
-      <c r="A43" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C43" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>852</v>
-      </c>
-      <c r="F43" s="5" t="s">
+      <c r="A43" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="3">
+        <v>2016</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G43" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="H43" s="6">
-        <v>500</v>
-      </c>
-      <c r="I43" s="10"/>
-      <c r="J43" s="11">
+      <c r="G43" s="4">
+        <v>14.82</v>
+      </c>
+      <c r="H43" s="4">
+        <v>267.614377</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="8">
         <v>1</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="4">
         <f>IF(ISNUMBER(I43),I43,IF(AND(ISNUMBER(G43),ISNUMBER(H43)),H43/G43,NA()))*J43</f>
-        <v>227.272727272727</v>
-      </c>
-      <c r="L43" s="11">
+        <v>18.0576502699055</v>
+      </c>
+      <c r="L43" s="8">
         <f>K43-1</f>
-        <v>226.272727272727</v>
-      </c>
-      <c r="M43" s="6">
+        <v>17.0576502699055</v>
+      </c>
+      <c r="M43" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N43" s="6">
+      <c r="N43" s="4">
         <f>M43*K43</f>
-        <v>113636.363636364</v>
-      </c>
-      <c r="O43" s="6">
+        <v>9028.82513495277</v>
+      </c>
+      <c r="O43" s="4">
         <f>N43-M43</f>
-        <v>113136.363636364</v>
-      </c>
-      <c r="P43" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="Q43" s="5" t="s">
-        <v>854</v>
-      </c>
-      <c r="R43" s="5" t="s">
-        <v>855</v>
+        <v>8528.82513495277</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>859</v>
       </c>
     </row>
     <row r="44" ht="105" customHeight="1" spans="1:18">
-      <c r="A44" s="5" t="s">
-        <v>856</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="C44" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>857</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>858</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>693</v>
-      </c>
-      <c r="G44" s="6">
-        <v>3</v>
-      </c>
-      <c r="H44" s="6">
-        <v>500</v>
-      </c>
-      <c r="I44" s="6"/>
-      <c r="J44" s="11">
+      <c r="A44" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2019</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G44" s="4">
         <v>1</v>
       </c>
-      <c r="K44" s="6">
+      <c r="H44" s="4">
+        <v>16.7</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="8">
+        <v>1</v>
+      </c>
+      <c r="K44" s="4">
         <f>IF(ISNUMBER(I44),I44,IF(AND(ISNUMBER(G44),ISNUMBER(H44)),H44/G44,NA()))*J44</f>
-        <v>166.666666666667</v>
-      </c>
-      <c r="L44" s="11">
+        <v>16.7</v>
+      </c>
+      <c r="L44" s="8">
         <f>K44-1</f>
-        <v>165.666666666667</v>
-      </c>
-      <c r="M44" s="6">
+        <v>15.7</v>
+      </c>
+      <c r="M44" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N44" s="6">
+      <c r="N44" s="4">
         <f>M44*K44</f>
-        <v>83333.3333333333</v>
-      </c>
-      <c r="O44" s="6">
+        <v>8350</v>
+      </c>
+      <c r="O44" s="4">
         <f>N44-M44</f>
-        <v>82833.3333333333</v>
-      </c>
-      <c r="P44" s="5" t="s">
-        <v>859</v>
-      </c>
-      <c r="Q44" s="5" t="s">
-        <v>860</v>
-      </c>
-      <c r="R44" s="5" t="s">
-        <v>861</v>
+        <v>7850</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="45" ht="105" customHeight="1" spans="1:18">
-      <c r="A45" s="5" t="s">
-        <v>862</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>539</v>
-      </c>
-      <c r="C45" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>863</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>864</v>
+      <c r="A45" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>868</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="G45" s="6">
+        <v>710</v>
+      </c>
+      <c r="G45" s="4">
+        <v>3</v>
+      </c>
+      <c r="H45" s="4">
+        <v>48</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="8">
         <v>1</v>
       </c>
-      <c r="H45" s="6">
-        <v>130</v>
-      </c>
-      <c r="I45" s="6"/>
-      <c r="J45" s="11">
-        <v>1</v>
-      </c>
-      <c r="K45" s="6">
+      <c r="K45" s="4">
         <f>IF(ISNUMBER(I45),I45,IF(AND(ISNUMBER(G45),ISNUMBER(H45)),H45/G45,NA()))*J45</f>
-        <v>130</v>
-      </c>
-      <c r="L45" s="11">
+        <v>16</v>
+      </c>
+      <c r="L45" s="8">
         <f>K45-1</f>
-        <v>129</v>
-      </c>
-      <c r="M45" s="6">
+        <v>15</v>
+      </c>
+      <c r="M45" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N45" s="6">
+      <c r="N45" s="4">
         <f>M45*K45</f>
-        <v>65000</v>
-      </c>
-      <c r="O45" s="6">
+        <v>8000</v>
+      </c>
+      <c r="O45" s="4">
         <f>N45-M45</f>
-        <v>64500</v>
-      </c>
-      <c r="P45" s="5" t="s">
-        <v>865</v>
-      </c>
-      <c r="Q45" s="5" t="s">
-        <v>866</v>
-      </c>
-      <c r="R45" s="5" t="s">
-        <v>867</v>
+        <v>7500</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="46" ht="105" customHeight="1" spans="1:18">
-      <c r="A46" s="3" t="s">
-        <v>868</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C46" s="3">
-        <v>2023</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>869</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="F46" s="3" t="s">
+      <c r="A46" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" s="5">
+        <v>2015</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="6">
+        <v>33.2592</v>
+      </c>
+      <c r="H46" s="6">
+        <v>518.49</v>
+      </c>
+      <c r="I46" s="6"/>
+      <c r="J46" s="10">
         <v>1</v>
       </c>
-      <c r="H46" s="4">
-        <v>100</v>
-      </c>
-      <c r="I46" s="4"/>
-      <c r="J46" s="8">
-        <v>1</v>
-      </c>
-      <c r="K46" s="4">
+      <c r="K46" s="6">
         <f>IF(ISNUMBER(I46),I46,IF(AND(ISNUMBER(G46),ISNUMBER(H46)),H46/G46,NA()))*J46</f>
-        <v>100</v>
-      </c>
-      <c r="L46" s="8">
+        <v>15.5893707605715</v>
+      </c>
+      <c r="L46" s="10">
         <f>K46-1</f>
-        <v>99</v>
-      </c>
-      <c r="M46" s="4">
+        <v>14.5893707605715</v>
+      </c>
+      <c r="M46" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N46" s="4">
+      <c r="N46" s="6">
         <f>M46*K46</f>
-        <v>50000</v>
-      </c>
-      <c r="O46" s="4">
+        <v>7794.68538028576</v>
+      </c>
+      <c r="O46" s="6">
         <f>N46-M46</f>
-        <v>49500</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>873</v>
+        <v>7294.68538028576</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="47" ht="105" customHeight="1" spans="1:18">
-      <c r="A47" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C47" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>875</v>
-      </c>
-      <c r="E47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>680</v>
-      </c>
-      <c r="G47" s="6">
-        <v>4</v>
-      </c>
-      <c r="H47" s="6">
-        <v>200</v>
-      </c>
-      <c r="I47" s="6"/>
-      <c r="J47" s="11">
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="3">
+        <v>2013</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="G47" s="4">
+        <v>15</v>
+      </c>
+      <c r="H47" s="4">
+        <v>160</v>
+      </c>
+      <c r="I47" s="4"/>
+      <c r="J47" s="8">
         <v>1</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="4">
         <f>IF(ISNUMBER(I47),I47,IF(AND(ISNUMBER(G47),ISNUMBER(H47)),H47/G47,NA()))*J47</f>
-        <v>50</v>
-      </c>
-      <c r="L47" s="11">
+        <v>10.6666666666667</v>
+      </c>
+      <c r="L47" s="8">
         <f>K47-1</f>
-        <v>49</v>
-      </c>
-      <c r="M47" s="6">
+        <v>9.66666666666667</v>
+      </c>
+      <c r="M47" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N47" s="6">
+      <c r="N47" s="4">
         <f>M47*K47</f>
-        <v>25000</v>
-      </c>
-      <c r="O47" s="6">
+        <v>5333.33333333333</v>
+      </c>
+      <c r="O47" s="4">
         <f>N47-M47</f>
-        <v>24500</v>
-      </c>
-      <c r="P47" s="5" t="s">
-        <v>877</v>
-      </c>
-      <c r="Q47" s="5" t="s">
+        <v>4833.33333333333</v>
+      </c>
+      <c r="P47" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="R47" s="5" t="s">
+      <c r="Q47" s="3" t="s">
         <v>879</v>
       </c>
+      <c r="R47" s="3" t="s">
+        <v>880</v>
+      </c>
     </row>
     <row r="48" ht="105" customHeight="1" spans="1:18">
-      <c r="A48" s="5" t="s">
-        <v>880</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>527</v>
-      </c>
-      <c r="C48" s="5">
-        <v>2023</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="F48" s="5" t="s">
+      <c r="A48" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C48" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G48" s="6">
-        <v>6</v>
-      </c>
-      <c r="H48" s="6">
-        <v>143</v>
-      </c>
-      <c r="I48" s="6"/>
-      <c r="J48" s="11">
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4">
+        <v>8</v>
+      </c>
+      <c r="J48" s="8">
         <v>1</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="4">
         <f>IF(ISNUMBER(I48),I48,IF(AND(ISNUMBER(G48),ISNUMBER(H48)),H48/G48,NA()))*J48</f>
-        <v>23.8333333333333</v>
-      </c>
-      <c r="L48" s="11">
+        <v>8</v>
+      </c>
+      <c r="L48" s="8">
         <f>K48-1</f>
-        <v>22.8333333333333</v>
-      </c>
-      <c r="M48" s="6">
+        <v>7</v>
+      </c>
+      <c r="M48" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N48" s="6">
+      <c r="N48" s="4">
         <f>M48*K48</f>
-        <v>11916.6666666667</v>
-      </c>
-      <c r="O48" s="6">
+        <v>4000</v>
+      </c>
+      <c r="O48" s="4">
         <f>N48-M48</f>
-        <v>11416.6666666667</v>
-      </c>
-      <c r="P48" s="5" t="s">
-        <v>881</v>
-      </c>
-      <c r="Q48" s="5" t="s">
-        <v>882</v>
-      </c>
-      <c r="R48" s="5" t="s">
+        <v>3500</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="49" ht="105" customHeight="1" spans="1:18">
+      <c r="A49" s="3" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="49" ht="105" customHeight="1" spans="1:18">
-      <c r="A49" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C49" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="C49" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>886</v>
-      </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G49" s="6">
+      <c r="G49" s="4">
+        <v>29.08</v>
+      </c>
+      <c r="H49" s="4">
+        <v>228.75</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="8">
         <v>1</v>
       </c>
-      <c r="H49" s="6">
-        <v>100</v>
-      </c>
-      <c r="I49" s="6"/>
-      <c r="J49" s="11">
-        <v>1</v>
-      </c>
-      <c r="K49" s="6">
+      <c r="K49" s="4">
         <f>IF(ISNUMBER(I49),I49,IF(AND(ISNUMBER(G49),ISNUMBER(H49)),H49/G49,NA()))*J49</f>
-        <v>100</v>
-      </c>
-      <c r="L49" s="11">
+        <v>7.8662310866575</v>
+      </c>
+      <c r="L49" s="8">
         <f>K49-1</f>
-        <v>99</v>
-      </c>
-      <c r="M49" s="6">
+        <v>6.8662310866575</v>
+      </c>
+      <c r="M49" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N49" s="6">
+      <c r="N49" s="4">
         <f>M49*K49</f>
-        <v>50000</v>
-      </c>
-      <c r="O49" s="6">
+        <v>3933.11554332875</v>
+      </c>
+      <c r="O49" s="4">
         <f>N49-M49</f>
-        <v>49500</v>
-      </c>
-      <c r="P49" s="5" t="s">
+        <v>3433.11554332875</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="R49" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="Q49" s="5" t="s">
+    </row>
+    <row r="50" ht="105" customHeight="1" spans="1:18">
+      <c r="A50" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="R49" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C50" s="3">
+        <v>2015</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="50" ht="105" customHeight="1" spans="1:18">
-      <c r="A50" s="5" t="s">
+      <c r="E50" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="C50" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6">
-        <v>80</v>
-      </c>
-      <c r="J50" s="11">
+      <c r="G50" s="4">
+        <v>66</v>
+      </c>
+      <c r="H50" s="4">
+        <v>290.1402496496</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="8">
         <v>1</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="4">
         <f>IF(ISNUMBER(I50),I50,IF(AND(ISNUMBER(G50),ISNUMBER(H50)),H50/G50,NA()))*J50</f>
-        <v>80</v>
-      </c>
-      <c r="L50" s="11">
+        <v>4.3960643886303</v>
+      </c>
+      <c r="L50" s="8">
         <f>K50-1</f>
-        <v>79</v>
-      </c>
-      <c r="M50" s="6">
+        <v>3.3960643886303</v>
+      </c>
+      <c r="M50" s="4">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N50" s="6">
+      <c r="N50" s="4">
         <f>M50*K50</f>
-        <v>40000</v>
-      </c>
-      <c r="O50" s="6">
+        <v>2198.03219431515</v>
+      </c>
+      <c r="O50" s="4">
         <f>N50-M50</f>
-        <v>39500</v>
-      </c>
-      <c r="P50" s="5" t="s">
+        <v>1698.03219431515</v>
+      </c>
+      <c r="P50" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="Q50" s="5" t="s">
+      <c r="Q50" s="3" t="s">
         <v>891</v>
       </c>
-      <c r="R50" s="5" t="s">
-        <v>742</v>
+      <c r="R50" s="3" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="51" ht="105" customHeight="1" spans="1:18">
-      <c r="A51" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="C51" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D51" s="3" t="s">
+      <c r="A51" s="5" t="s">
         <v>893</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="F51" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="5">
+        <v>2015</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4">
-        <v>60</v>
-      </c>
-      <c r="J51" s="8">
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J51" s="10">
         <v>1</v>
       </c>
-      <c r="K51" s="4">
+      <c r="K51" s="6">
         <f>IF(ISNUMBER(I51),I51,IF(AND(ISNUMBER(G51),ISNUMBER(H51)),H51/G51,NA()))*J51</f>
-        <v>60</v>
-      </c>
-      <c r="L51" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="L51" s="10">
         <f>K51-1</f>
-        <v>59</v>
-      </c>
-      <c r="M51" s="4">
+        <v>-0.9</v>
+      </c>
+      <c r="M51" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N51" s="4">
+      <c r="N51" s="6">
         <f>M51*K51</f>
-        <v>30000</v>
-      </c>
-      <c r="O51" s="4">
+        <v>50</v>
+      </c>
+      <c r="O51" s="6">
         <f>N51-M51</f>
-        <v>29500</v>
-      </c>
-      <c r="P51" s="3" t="s">
+        <v>-450</v>
+      </c>
+      <c r="P51" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="Q51" s="3" t="s">
-        <v>894</v>
-      </c>
-      <c r="R51" s="3" t="s">
-        <v>733</v>
+      <c r="Q51" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="52" ht="105" customHeight="1" spans="1:18">
       <c r="A52" s="5" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>515</v>
+        <v>288</v>
       </c>
       <c r="C52" s="5">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>686</v>
+        <v>900</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G52" s="6">
-        <v>3</v>
-      </c>
-      <c r="H52" s="6">
-        <v>150</v>
-      </c>
-      <c r="I52" s="6"/>
-      <c r="J52" s="11">
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J52" s="10">
         <v>1</v>
       </c>
       <c r="K52" s="6">
         <f>IF(ISNUMBER(I52),I52,IF(AND(ISNUMBER(G52),ISNUMBER(H52)),H52/G52,NA()))*J52</f>
-        <v>50</v>
-      </c>
-      <c r="L52" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="L52" s="10">
         <f>K52-1</f>
-        <v>49</v>
+        <v>-0.9</v>
       </c>
       <c r="M52" s="6">
         <f>$B$2</f>
@@ -10291,58 +10295,56 @@
       </c>
       <c r="N52" s="6">
         <f>M52*K52</f>
-        <v>25000</v>
+        <v>50</v>
       </c>
       <c r="O52" s="6">
         <f>N52-M52</f>
-        <v>24500</v>
+        <v>-450</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>897</v>
+        <v>687</v>
       </c>
       <c r="Q52" s="5" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="R52" s="5" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="53" ht="105" customHeight="1" spans="1:18">
       <c r="A53" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C53" s="3">
+        <v>2020</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>900</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="C53" s="3">
-        <v>2024</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>902</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G53" s="4">
-        <v>2.8</v>
-      </c>
-      <c r="H53" s="4">
-        <v>77.4</v>
-      </c>
-      <c r="I53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4">
+        <v>0.1</v>
+      </c>
       <c r="J53" s="8">
         <v>1</v>
       </c>
       <c r="K53" s="4">
         <f>IF(ISNUMBER(I53),I53,IF(AND(ISNUMBER(G53),ISNUMBER(H53)),H53/G53,NA()))*J53</f>
-        <v>27.6428571428571</v>
+        <v>0.1</v>
       </c>
       <c r="L53" s="8">
         <f>K53-1</f>
-        <v>26.6428571428571</v>
+        <v>-0.9</v>
       </c>
       <c r="M53" s="4">
         <f>$B$2</f>
@@ -10350,58 +10352,56 @@
       </c>
       <c r="N53" s="4">
         <f>M53*K53</f>
-        <v>13821.4285714286</v>
+        <v>50</v>
       </c>
       <c r="O53" s="4">
         <f>N53-M53</f>
-        <v>13321.4285714286</v>
+        <v>-450</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>903</v>
+        <v>687</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>904</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
     </row>
     <row r="54" ht="105" customHeight="1" spans="1:18">
       <c r="A54" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C54" s="5">
+        <v>2020</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>906</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="C54" s="5">
-        <v>2024</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>907</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>908</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G54" s="6">
-        <v>10</v>
-      </c>
-      <c r="H54" s="6">
-        <v>200</v>
-      </c>
-      <c r="I54" s="6"/>
-      <c r="J54" s="11">
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J54" s="10">
         <v>1</v>
       </c>
       <c r="K54" s="6">
         <f>IF(ISNUMBER(I54),I54,IF(AND(ISNUMBER(G54),ISNUMBER(H54)),H54/G54,NA()))*J54</f>
-        <v>20</v>
-      </c>
-      <c r="L54" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="L54" s="10">
         <f>K54-1</f>
-        <v>19</v>
+        <v>-0.9</v>
       </c>
       <c r="M54" s="6">
         <f>$B$2</f>
@@ -10409,77 +10409,77 @@
       </c>
       <c r="N54" s="6">
         <f>M54*K54</f>
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="O54" s="6">
         <f>N54-M54</f>
-        <v>9500</v>
+        <v>-450</v>
       </c>
       <c r="P54" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q54" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="R54" s="5" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="55" ht="105" customHeight="1" spans="1:18">
+      <c r="A55" s="5" t="s">
         <v>909</v>
       </c>
-      <c r="Q54" s="5" t="s">
+      <c r="B55" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C55" s="5">
+        <v>2021</v>
+      </c>
+      <c r="D55" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="R54" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="55" ht="105" customHeight="1" spans="1:18">
-      <c r="A55" s="3" t="s">
-        <v>912</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="C55" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>913</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4">
-        <v>8</v>
-      </c>
-      <c r="J55" s="8">
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J55" s="10">
         <v>1</v>
       </c>
-      <c r="K55" s="4">
+      <c r="K55" s="6">
         <f>IF(ISNUMBER(I55),I55,IF(AND(ISNUMBER(G55),ISNUMBER(H55)),H55/G55,NA()))*J55</f>
-        <v>8</v>
-      </c>
-      <c r="L55" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="L55" s="10">
         <f>K55-1</f>
-        <v>7</v>
-      </c>
-      <c r="M55" s="4">
+        <v>-0.9</v>
+      </c>
+      <c r="M55" s="6">
         <f>$B$2</f>
         <v>500</v>
       </c>
-      <c r="N55" s="4">
+      <c r="N55" s="6">
         <f>M55*K55</f>
-        <v>4000</v>
-      </c>
-      <c r="O55" s="4">
+        <v>50</v>
+      </c>
+      <c r="O55" s="6">
         <f>N55-M55</f>
-        <v>3500</v>
-      </c>
-      <c r="P55" s="3" t="s">
+        <v>-450</v>
+      </c>
+      <c r="P55" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="Q55" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="R55" s="3" t="s">
-        <v>733</v>
+      <c r="Q55" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="R55" s="5" t="s">
+        <v>913</v>
       </c>
     </row>
     <row r="56" ht="105" customHeight="1" spans="1:18">
@@ -10496,7 +10496,7 @@
         <v>915</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>680</v>
@@ -10508,14 +10508,14 @@
       <c r="I56" s="6">
         <v>0.1</v>
       </c>
-      <c r="J56" s="11">
+      <c r="J56" s="10">
         <v>1</v>
       </c>
       <c r="K56" s="6">
         <f>IF(ISNUMBER(I56),I56,IF(AND(ISNUMBER(G56),ISNUMBER(H56)),H56/G56,NA()))*J56</f>
         <v>0.1</v>
       </c>
-      <c r="L56" s="11">
+      <c r="L56" s="10">
         <f>K56-1</f>
         <v>-0.9</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>-450</v>
       </c>
       <c r="P56" s="5" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="Q56" s="5" t="s">
         <v>916</v>
@@ -10544,7 +10544,7 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A6:R56" etc:filterBottomFollowUsedRange="0">
     <sortState ref="A7:R56">
-      <sortCondition ref="C6"/>
+      <sortCondition ref="K6" descending="1"/>
     </sortState>
     <extLst/>
   </autoFilter>
@@ -10628,7 +10628,7 @@
     </row>
     <row r="8" ht="140" customHeight="1" spans="1:11">
       <c r="A8" s="3" t="s">
-        <v>729</v>
+        <v>677</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>160</v>
@@ -10637,7 +10637,7 @@
         <v>928</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>731</v>
+        <v>679</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>929</v>
@@ -10652,7 +10652,7 @@
         <v>931</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>733</v>
+        <v>683</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>932</v>
@@ -10663,7 +10663,7 @@
     </row>
     <row r="9" ht="140" customHeight="1" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>842</v>
+        <v>801</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>440</v>
@@ -10672,7 +10672,7 @@
         <v>934</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>935</v>
@@ -10687,7 +10687,7 @@
         <v>937</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>844</v>
+        <v>803</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>938</v>
@@ -10698,7 +10698,7 @@
     </row>
     <row r="10" ht="140" customHeight="1" spans="1:11">
       <c r="A10" s="3" t="s">
-        <v>912</v>
+        <v>881</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>616</v>
@@ -10707,7 +10707,7 @@
         <v>939</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>731</v>
+        <v>679</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>940</v>
@@ -10722,7 +10722,7 @@
         <v>931</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>733</v>
+        <v>683</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>941</v>
@@ -10733,7 +10733,7 @@
     </row>
     <row r="11" ht="140" customHeight="1" spans="1:11">
       <c r="A11" s="5" t="s">
-        <v>890</v>
+        <v>760</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>551</v>
@@ -10742,7 +10742,7 @@
         <v>942</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>943</v>
@@ -10757,7 +10757,7 @@
         <v>937</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>945</v>
@@ -10768,7 +10768,7 @@
     </row>
     <row r="12" ht="140" customHeight="1" spans="1:11">
       <c r="A12" s="3" t="s">
-        <v>702</v>
+        <v>720</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>69</v>
@@ -10777,7 +10777,7 @@
         <v>946</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>947</v>
@@ -10790,7 +10790,7 @@
         <v>949</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>704</v>
+        <v>723</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>950</v>
@@ -10801,7 +10801,7 @@
     </row>
     <row r="13" ht="140" customHeight="1" spans="1:11">
       <c r="A13" s="5" t="s">
-        <v>697</v>
+        <v>804</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>56</v>
@@ -10810,7 +10810,7 @@
         <v>952</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>953</v>
@@ -10823,7 +10823,7 @@
         <v>949</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>701</v>
+        <v>806</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>955</v>
@@ -10834,7 +10834,7 @@
     </row>
     <row r="14" ht="140" customHeight="1" spans="1:11">
       <c r="A14" s="3" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>326</v>
@@ -10843,7 +10843,7 @@
         <v>956</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>817</v>
+        <v>852</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>957</v>
@@ -10858,7 +10858,7 @@
         <v>959</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>819</v>
+        <v>854</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>960</v>
@@ -10869,7 +10869,7 @@
     </row>
     <row r="15" ht="140" customHeight="1" spans="1:11">
       <c r="A15" s="5" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>263</v>
@@ -10878,7 +10878,7 @@
         <v>962</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>963</v>
@@ -10893,7 +10893,7 @@
         <v>965</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>966</v>
@@ -10904,7 +10904,7 @@
     </row>
     <row r="16" ht="140" customHeight="1" spans="1:11">
       <c r="A16" s="3" t="s">
-        <v>719</v>
+        <v>888</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>629</v>
@@ -10913,7 +10913,7 @@
         <v>967</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>721</v>
+        <v>890</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>968</v>
@@ -10928,7 +10928,7 @@
         <v>970</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>723</v>
+        <v>892</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>971</v>
@@ -10939,7 +10939,7 @@
     </row>
     <row r="17" ht="140" customHeight="1" spans="1:11">
       <c r="A17" s="5" t="s">
-        <v>845</v>
+        <v>807</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>453</v>
@@ -10948,7 +10948,7 @@
         <v>972</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>847</v>
+        <v>809</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>973</v>
@@ -10963,7 +10963,7 @@
         <v>975</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>850</v>
+        <v>812</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>976</v>
@@ -10974,7 +10974,7 @@
     </row>
     <row r="18" ht="140" customHeight="1" spans="1:11">
       <c r="A18" s="3" t="s">
-        <v>820</v>
+        <v>883</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>339</v>
@@ -10983,7 +10983,7 @@
         <v>977</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>822</v>
+        <v>885</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>978</v>
@@ -10998,7 +10998,7 @@
         <v>980</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>824</v>
+        <v>887</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>981</v>
@@ -11009,7 +11009,7 @@
     </row>
     <row r="19" ht="140" customHeight="1" spans="1:11">
       <c r="A19" s="5" t="s">
-        <v>851</v>
+        <v>701</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>466</v>
@@ -11018,7 +11018,7 @@
         <v>982</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>852</v>
+        <v>703</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>983</v>
@@ -11031,7 +11031,7 @@
         <v>931</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>855</v>
+        <v>706</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>985</v>
@@ -11042,7 +11042,7 @@
     </row>
     <row r="20" ht="140" customHeight="1" spans="1:11">
       <c r="A20" s="3" t="s">
-        <v>868</v>
+        <v>743</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>478</v>
@@ -11051,7 +11051,7 @@
         <v>986</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>870</v>
+        <v>745</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>987</v>
@@ -11064,7 +11064,7 @@
         <v>931</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>873</v>
+        <v>748</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>989</v>
@@ -11075,7 +11075,7 @@
     </row>
     <row r="21" ht="140" customHeight="1" spans="1:11">
       <c r="A21" s="5" t="s">
-        <v>906</v>
+        <v>844</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>565</v>
@@ -11084,7 +11084,7 @@
         <v>990</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>908</v>
+        <v>846</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>991</v>
@@ -11097,7 +11097,7 @@
         <v>931</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>911</v>
+        <v>849</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>993</v>
@@ -11108,7 +11108,7 @@
     </row>
     <row r="22" ht="140" customHeight="1" spans="1:11">
       <c r="A22" s="3" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>16</v>
@@ -11117,7 +11117,7 @@
         <v>994</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>995</v>
@@ -11132,7 +11132,7 @@
         <v>931</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>997</v>
@@ -11143,7 +11143,7 @@
     </row>
     <row r="23" ht="140" customHeight="1" spans="1:11">
       <c r="A23" s="5" t="s">
-        <v>884</v>
+        <v>749</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>577</v>
@@ -11152,7 +11152,7 @@
         <v>998</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>886</v>
+        <v>751</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>999</v>
@@ -11167,7 +11167,7 @@
         <v>931</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>1001</v>
@@ -11178,7 +11178,7 @@
     </row>
     <row r="24" ht="140" customHeight="1" spans="1:11">
       <c r="A24" s="3" t="s">
-        <v>892</v>
+        <v>767</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>590</v>
@@ -11187,7 +11187,7 @@
         <v>1002</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>731</v>
+        <v>679</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>1003</v>
@@ -11202,7 +11202,7 @@
         <v>931</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>733</v>
+        <v>683</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>1005</v>
@@ -11213,7 +11213,7 @@
     </row>
     <row r="25" ht="140" customHeight="1" spans="1:11">
       <c r="A25" s="5" t="s">
-        <v>874</v>
+        <v>776</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>490</v>
@@ -11222,7 +11222,7 @@
         <v>1006</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>876</v>
+        <v>778</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>1007</v>
@@ -11235,7 +11235,7 @@
         <v>931</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>879</v>
+        <v>781</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>1009</v>
@@ -11246,7 +11246,7 @@
     </row>
     <row r="26" ht="140" customHeight="1" spans="1:11">
       <c r="A26" s="3" t="s">
-        <v>747</v>
+        <v>817</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>173</v>
@@ -11255,7 +11255,7 @@
         <v>1010</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>707</v>
+        <v>789</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>1011</v>
@@ -11270,7 +11270,7 @@
         <v>949</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>750</v>
+        <v>820</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>1013</v>
@@ -11281,7 +11281,7 @@
     </row>
     <row r="27" ht="140" customHeight="1" spans="1:11">
       <c r="A27" s="5" t="s">
-        <v>705</v>
+        <v>787</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>81</v>
@@ -11290,7 +11290,7 @@
         <v>1014</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>707</v>
+        <v>789</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>1015</v>
@@ -11305,7 +11305,7 @@
         <v>949</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>709</v>
+        <v>791</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>1017</v>
@@ -11316,7 +11316,7 @@
     </row>
     <row r="28" ht="140" customHeight="1" spans="1:11">
       <c r="A28" s="3" t="s">
-        <v>762</v>
+        <v>855</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>94</v>
@@ -11325,7 +11325,7 @@
         <v>1018</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>707</v>
+        <v>789</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>1019</v>
@@ -11351,7 +11351,7 @@
     </row>
     <row r="29" ht="140" customHeight="1" spans="1:11">
       <c r="A29" s="5" t="s">
-        <v>743</v>
+        <v>813</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>186</v>
@@ -11360,7 +11360,7 @@
         <v>1023</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>1024</v>
@@ -11373,7 +11373,7 @@
         <v>949</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>746</v>
+        <v>816</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>1026</v>
@@ -11384,7 +11384,7 @@
     </row>
     <row r="30" ht="140" customHeight="1" spans="1:11">
       <c r="A30" s="3" t="s">
-        <v>690</v>
+        <v>876</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>31</v>
@@ -11393,7 +11393,7 @@
         <v>1027</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>1028</v>
@@ -11406,7 +11406,7 @@
         <v>949</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>696</v>
+        <v>880</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>1030</v>
@@ -11417,7 +11417,7 @@
     </row>
     <row r="31" ht="140" customHeight="1" spans="1:11">
       <c r="A31" s="5" t="s">
-        <v>788</v>
+        <v>898</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>288</v>
@@ -11426,7 +11426,7 @@
         <v>1031</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>790</v>
+        <v>900</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>1032</v>
@@ -11439,7 +11439,7 @@
         <v>949</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>792</v>
+        <v>902</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>1034</v>
@@ -11450,7 +11450,7 @@
     </row>
     <row r="32" ht="140" customHeight="1" spans="1:11">
       <c r="A32" s="3" t="s">
-        <v>825</v>
+        <v>903</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>353</v>
@@ -11459,7 +11459,7 @@
         <v>1035</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>790</v>
+        <v>900</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>1036</v>
@@ -11472,7 +11472,7 @@
         <v>949</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>792</v>
+        <v>902</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>1037</v>
@@ -11483,7 +11483,7 @@
     </row>
     <row r="33" ht="140" customHeight="1" spans="1:11">
       <c r="A33" s="5" t="s">
-        <v>827</v>
+        <v>905</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>364</v>
@@ -11492,7 +11492,7 @@
         <v>1038</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>828</v>
+        <v>906</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>1039</v>
@@ -11505,7 +11505,7 @@
         <v>949</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>830</v>
+        <v>908</v>
       </c>
       <c r="J33" s="5" t="s">
         <v>1041</v>
@@ -11516,7 +11516,7 @@
     </row>
     <row r="34" ht="140" customHeight="1" spans="1:11">
       <c r="A34" s="3" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>198</v>
@@ -11525,7 +11525,7 @@
         <v>1042</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>1043</v>
@@ -11540,7 +11540,7 @@
         <v>937</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>1045</v>
@@ -11560,7 +11560,7 @@
         <v>1046</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>1047</v>
@@ -11586,7 +11586,7 @@
     </row>
     <row r="36" ht="140" customHeight="1" spans="1:11">
       <c r="A36" s="3" t="s">
-        <v>756</v>
+        <v>832</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>212</v>
@@ -11595,7 +11595,7 @@
         <v>1050</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>758</v>
+        <v>834</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>1051</v>
@@ -11608,7 +11608,7 @@
         <v>1053</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>761</v>
+        <v>837</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>1054</v>
@@ -11619,7 +11619,7 @@
     </row>
     <row r="37" ht="140" customHeight="1" spans="1:11">
       <c r="A37" s="5" t="s">
-        <v>751</v>
+        <v>821</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>224</v>
@@ -11628,7 +11628,7 @@
         <v>1055</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>753</v>
+        <v>823</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>1056</v>
@@ -11643,7 +11643,7 @@
         <v>1058</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>755</v>
+        <v>825</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>1059</v>
@@ -11654,7 +11654,7 @@
     </row>
     <row r="38" ht="140" customHeight="1" spans="1:11">
       <c r="A38" s="3" t="s">
-        <v>772</v>
+        <v>796</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>276</v>
@@ -11663,7 +11663,7 @@
         <v>1060</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>774</v>
+        <v>798</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>1061</v>
@@ -11676,7 +11676,7 @@
         <v>1063</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>776</v>
+        <v>800</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>1064</v>
@@ -11687,7 +11687,7 @@
     </row>
     <row r="39" ht="140" customHeight="1" spans="1:11">
       <c r="A39" s="5" t="s">
-        <v>813</v>
+        <v>842</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>376</v>
@@ -11696,7 +11696,7 @@
         <v>1065</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>1066</v>
@@ -11711,7 +11711,7 @@
         <v>937</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>1068</v>
@@ -11722,7 +11722,7 @@
     </row>
     <row r="40" ht="140" customHeight="1" spans="1:11">
       <c r="A40" s="3" t="s">
-        <v>831</v>
+        <v>737</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>415</v>
@@ -11731,7 +11731,7 @@
         <v>1069</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>833</v>
+        <v>739</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>1070</v>
@@ -11746,7 +11746,7 @@
         <v>1072</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>836</v>
+        <v>742</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>1073</v>
@@ -11757,7 +11757,7 @@
     </row>
     <row r="41" ht="140" customHeight="1" spans="1:11">
       <c r="A41" s="5" t="s">
-        <v>837</v>
+        <v>909</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>428</v>
@@ -11766,7 +11766,7 @@
         <v>1074</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>839</v>
+        <v>911</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>1075</v>
@@ -11779,7 +11779,7 @@
         <v>1077</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>841</v>
+        <v>913</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>1078</v>
@@ -11790,7 +11790,7 @@
     </row>
     <row r="42" ht="140" customHeight="1" spans="1:11">
       <c r="A42" s="3" t="s">
-        <v>783</v>
+        <v>866</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>237</v>
@@ -11825,7 +11825,7 @@
     </row>
     <row r="43" ht="140" customHeight="1" spans="1:11">
       <c r="A43" s="5" t="s">
-        <v>724</v>
+        <v>893</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>107</v>
@@ -11834,7 +11834,7 @@
         <v>1085</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>726</v>
+        <v>895</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>1086</v>
@@ -11847,7 +11847,7 @@
         <v>1088</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>728</v>
+        <v>897</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>1089</v>
@@ -11858,7 +11858,7 @@
     </row>
     <row r="44" ht="140" customHeight="1" spans="1:11">
       <c r="A44" s="3" t="s">
-        <v>804</v>
+        <v>690</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>389</v>
@@ -11893,7 +11893,7 @@
     </row>
     <row r="45" ht="140" customHeight="1" spans="1:11">
       <c r="A45" s="5" t="s">
-        <v>714</v>
+        <v>871</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>120</v>
@@ -11928,7 +11928,7 @@
     </row>
     <row r="46" ht="140" customHeight="1" spans="1:11">
       <c r="A46" s="3" t="s">
-        <v>809</v>
+        <v>728</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>402</v>
@@ -11963,7 +11963,7 @@
     </row>
     <row r="47" ht="140" customHeight="1" spans="1:11">
       <c r="A47" s="5" t="s">
-        <v>856</v>
+        <v>707</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>502</v>
@@ -11998,7 +11998,7 @@
     </row>
     <row r="48" ht="140" customHeight="1" spans="1:11">
       <c r="A48" s="3" t="s">
-        <v>793</v>
+        <v>684</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>312</v>
@@ -12033,7 +12033,7 @@
     </row>
     <row r="49" ht="140" customHeight="1" spans="1:11">
       <c r="A49" s="5" t="s">
-        <v>895</v>
+        <v>782</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>515</v>
@@ -12042,7 +12042,7 @@
         <v>1123</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>686</v>
+        <v>764</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>1124</v>
@@ -12066,7 +12066,7 @@
     </row>
     <row r="50" ht="140" customHeight="1" spans="1:11">
       <c r="A50" s="3" t="s">
-        <v>684</v>
+        <v>762</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>44</v>
@@ -12075,7 +12075,7 @@
         <v>1129</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>686</v>
+        <v>764</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>1130</v>
@@ -12088,7 +12088,7 @@
         <v>1132</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>689</v>
+        <v>766</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>1133</v>
@@ -12099,7 +12099,7 @@
     </row>
     <row r="51" ht="140" customHeight="1" spans="1:11">
       <c r="A51" s="5" t="s">
-        <v>880</v>
+        <v>838</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>527</v>
@@ -12108,7 +12108,7 @@
         <v>982</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>1134</v>
@@ -12132,7 +12132,7 @@
     </row>
     <row r="52" ht="140" customHeight="1" spans="1:11">
       <c r="A52" s="3" t="s">
-        <v>900</v>
+        <v>826</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>603</v>
@@ -12141,7 +12141,7 @@
         <v>1139</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>686</v>
+        <v>764</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>1140</v>
@@ -12165,7 +12165,7 @@
     </row>
     <row r="53" ht="140" customHeight="1" spans="1:11">
       <c r="A53" s="5" t="s">
-        <v>862</v>
+        <v>714</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>539</v>
@@ -12174,7 +12174,7 @@
         <v>1145</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>864</v>
+        <v>716</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>1146</v>
@@ -12187,7 +12187,7 @@
         <v>931</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>867</v>
+        <v>719</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>1148</v>
@@ -12198,7 +12198,7 @@
     </row>
     <row r="54" ht="140" customHeight="1" spans="1:11">
       <c r="A54" s="3" t="s">
-        <v>798</v>
+        <v>860</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>134</v>
@@ -12207,7 +12207,7 @@
         <v>1149</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>686</v>
+        <v>764</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>1150</v>
@@ -12231,7 +12231,7 @@
     </row>
     <row r="55" ht="140" customHeight="1" spans="1:11">
       <c r="A55" s="5" t="s">
-        <v>710</v>
+        <v>792</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>148</v>
@@ -12240,7 +12240,7 @@
         <v>1155</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>686</v>
+        <v>764</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>1156</v>
@@ -12253,7 +12253,7 @@
         <v>1158</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>713</v>
+        <v>795</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>1159</v>
@@ -12264,7 +12264,7 @@
     </row>
     <row r="56" ht="140" customHeight="1" spans="1:11">
       <c r="A56" s="3" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>250</v>
@@ -12273,7 +12273,7 @@
         <v>1023</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>1160</v>
@@ -12286,7 +12286,7 @@
         <v>1162</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>1163</v>
@@ -12297,7 +12297,7 @@
     </row>
     <row r="57" ht="140" customHeight="1" spans="1:11">
       <c r="A57" s="5" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>300</v>
@@ -12306,7 +12306,7 @@
         <v>1164</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>1165</v>
@@ -12319,7 +12319,7 @@
         <v>1167</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>1168</v>
